--- a/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/alle groepen/bestemmingen/restdag/Ontpl_totaal_Auto_OV.xlsx
@@ -385,13 +385,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>13739</v>
+        <v>13743</v>
       </c>
       <c r="C2">
-        <v>22721</v>
+        <v>22724</v>
       </c>
       <c r="D2">
-        <v>47704</v>
+        <v>47708</v>
       </c>
       <c r="E2">
         <v>68526</v>
@@ -402,13 +402,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>15011</v>
+        <v>15017</v>
       </c>
       <c r="C3">
-        <v>25730</v>
+        <v>25734</v>
       </c>
       <c r="D3">
-        <v>52930</v>
+        <v>52934</v>
       </c>
       <c r="E3">
         <v>73687</v>
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>12407</v>
+        <v>12411</v>
       </c>
       <c r="C4">
-        <v>21987</v>
+        <v>21990</v>
       </c>
       <c r="D4">
-        <v>48987</v>
+        <v>48991</v>
       </c>
       <c r="E4">
-        <v>69834</v>
+        <v>69844</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12407</v>
+        <v>12411</v>
       </c>
       <c r="C5">
-        <v>21987</v>
+        <v>21990</v>
       </c>
       <c r="D5">
-        <v>48987</v>
+        <v>48991</v>
       </c>
       <c r="E5">
-        <v>69834</v>
+        <v>69844</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12407</v>
+        <v>12411</v>
       </c>
       <c r="C6">
-        <v>21987</v>
+        <v>21990</v>
       </c>
       <c r="D6">
-        <v>48987</v>
+        <v>48991</v>
       </c>
       <c r="E6">
-        <v>69834</v>
+        <v>69844</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="C7">
-        <v>20285</v>
+        <v>20322</v>
       </c>
       <c r="D7">
-        <v>44512</v>
+        <v>44544</v>
       </c>
       <c r="E7">
-        <v>64438</v>
+        <v>64483</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="C8">
-        <v>20285</v>
+        <v>20322</v>
       </c>
       <c r="D8">
-        <v>44512</v>
+        <v>44544</v>
       </c>
       <c r="E8">
-        <v>64438</v>
+        <v>64483</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>9789</v>
+        <v>9860</v>
       </c>
       <c r="C9">
-        <v>16308</v>
+        <v>16389</v>
       </c>
       <c r="D9">
-        <v>36952</v>
+        <v>37031</v>
       </c>
       <c r="E9">
-        <v>56125</v>
+        <v>56253</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="C10">
-        <v>20285</v>
+        <v>20322</v>
       </c>
       <c r="D10">
-        <v>44512</v>
+        <v>44544</v>
       </c>
       <c r="E10">
-        <v>64438</v>
+        <v>64483</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="C11">
-        <v>20285</v>
+        <v>20322</v>
       </c>
       <c r="D11">
-        <v>44512</v>
+        <v>44544</v>
       </c>
       <c r="E11">
-        <v>64438</v>
+        <v>64483</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,13 +555,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>11817</v>
+        <v>11822</v>
       </c>
       <c r="C12">
-        <v>20946</v>
+        <v>20949</v>
       </c>
       <c r="D12">
-        <v>47081</v>
+        <v>47084</v>
       </c>
       <c r="E12">
         <v>68731</v>
@@ -572,13 +572,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>15011</v>
+        <v>15017</v>
       </c>
       <c r="C13">
-        <v>25730</v>
+        <v>25734</v>
       </c>
       <c r="D13">
-        <v>52930</v>
+        <v>52934</v>
       </c>
       <c r="E13">
         <v>73687</v>
@@ -589,13 +589,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>11817</v>
+        <v>11822</v>
       </c>
       <c r="C14">
-        <v>20946</v>
+        <v>20949</v>
       </c>
       <c r="D14">
-        <v>47081</v>
+        <v>47084</v>
       </c>
       <c r="E14">
         <v>68731</v>
@@ -606,16 +606,16 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>12059</v>
+        <v>12099</v>
       </c>
       <c r="C15">
-        <v>20285</v>
+        <v>20322</v>
       </c>
       <c r="D15">
-        <v>44512</v>
+        <v>44544</v>
       </c>
       <c r="E15">
-        <v>64438</v>
+        <v>64483</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -623,16 +623,16 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="C16">
-        <v>18074</v>
+        <v>18111</v>
       </c>
       <c r="D16">
-        <v>39928</v>
+        <v>39969</v>
       </c>
       <c r="E16">
-        <v>58959</v>
+        <v>58993</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -640,13 +640,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>11817</v>
+        <v>11822</v>
       </c>
       <c r="C17">
-        <v>20946</v>
+        <v>20949</v>
       </c>
       <c r="D17">
-        <v>47081</v>
+        <v>47084</v>
       </c>
       <c r="E17">
         <v>68731</v>
@@ -657,13 +657,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>15011</v>
+        <v>15017</v>
       </c>
       <c r="C18">
-        <v>25730</v>
+        <v>25734</v>
       </c>
       <c r="D18">
-        <v>52930</v>
+        <v>52934</v>
       </c>
       <c r="E18">
         <v>73687</v>
@@ -674,16 +674,16 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="C19">
-        <v>18074</v>
+        <v>18111</v>
       </c>
       <c r="D19">
-        <v>39928</v>
+        <v>39969</v>
       </c>
       <c r="E19">
-        <v>58959</v>
+        <v>58993</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -691,16 +691,16 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="C20">
-        <v>18074</v>
+        <v>18111</v>
       </c>
       <c r="D20">
-        <v>39928</v>
+        <v>39969</v>
       </c>
       <c r="E20">
-        <v>58959</v>
+        <v>58993</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -708,16 +708,16 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>10987</v>
+        <v>11017</v>
       </c>
       <c r="C21">
-        <v>18074</v>
+        <v>18111</v>
       </c>
       <c r="D21">
-        <v>39928</v>
+        <v>39969</v>
       </c>
       <c r="E21">
-        <v>58959</v>
+        <v>58993</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -725,16 +725,16 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>17819</v>
+        <v>17901</v>
       </c>
       <c r="C22">
-        <v>32707</v>
+        <v>32750</v>
       </c>
       <c r="D22">
-        <v>61568</v>
+        <v>61590</v>
       </c>
       <c r="E22">
-        <v>78952</v>
+        <v>78977</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -742,13 +742,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>13739</v>
+        <v>13743</v>
       </c>
       <c r="C23">
-        <v>22721</v>
+        <v>22724</v>
       </c>
       <c r="D23">
-        <v>47704</v>
+        <v>47708</v>
       </c>
       <c r="E23">
         <v>68526</v>
@@ -759,16 +759,16 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>9659</v>
+        <v>9660</v>
       </c>
       <c r="C24">
         <v>16757</v>
       </c>
       <c r="D24">
-        <v>39198</v>
+        <v>39202</v>
       </c>
       <c r="E24">
-        <v>59336</v>
+        <v>59342</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -776,16 +776,16 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>9659</v>
+        <v>9660</v>
       </c>
       <c r="C25">
         <v>16757</v>
       </c>
       <c r="D25">
-        <v>39198</v>
+        <v>39202</v>
       </c>
       <c r="E25">
-        <v>59336</v>
+        <v>59342</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -793,16 +793,16 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>9659</v>
+        <v>9660</v>
       </c>
       <c r="C26">
         <v>16757</v>
       </c>
       <c r="D26">
-        <v>39198</v>
+        <v>39202</v>
       </c>
       <c r="E26">
-        <v>59336</v>
+        <v>59342</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -810,16 +810,16 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>13244</v>
+        <v>13250</v>
       </c>
       <c r="C27">
-        <v>23364</v>
+        <v>23367</v>
       </c>
       <c r="D27">
-        <v>50549</v>
+        <v>50557</v>
       </c>
       <c r="E27">
-        <v>70859</v>
+        <v>70872</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -827,16 +827,16 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>13244</v>
+        <v>13250</v>
       </c>
       <c r="C28">
-        <v>23364</v>
+        <v>23367</v>
       </c>
       <c r="D28">
-        <v>50549</v>
+        <v>50557</v>
       </c>
       <c r="E28">
-        <v>70859</v>
+        <v>70872</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -844,16 +844,16 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>13244</v>
+        <v>13250</v>
       </c>
       <c r="C29">
-        <v>23364</v>
+        <v>23367</v>
       </c>
       <c r="D29">
-        <v>50549</v>
+        <v>50557</v>
       </c>
       <c r="E29">
-        <v>70859</v>
+        <v>70872</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -861,16 +861,16 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>22681</v>
+        <v>22827</v>
       </c>
       <c r="C30">
-        <v>34261</v>
+        <v>34389</v>
       </c>
       <c r="D30">
-        <v>54016</v>
+        <v>54246</v>
       </c>
       <c r="E30">
-        <v>68894</v>
+        <v>69059</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -878,16 +878,16 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>22681</v>
+        <v>22827</v>
       </c>
       <c r="C31">
-        <v>34261</v>
+        <v>34389</v>
       </c>
       <c r="D31">
-        <v>54016</v>
+        <v>54246</v>
       </c>
       <c r="E31">
-        <v>68894</v>
+        <v>69059</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -895,16 +895,16 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>26831</v>
+        <v>26902</v>
       </c>
       <c r="C32">
-        <v>39578</v>
+        <v>39644</v>
       </c>
       <c r="D32">
-        <v>60329</v>
+        <v>60438</v>
       </c>
       <c r="E32">
-        <v>74663</v>
+        <v>74718</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -912,16 +912,16 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>22681</v>
+        <v>22827</v>
       </c>
       <c r="C33">
-        <v>34261</v>
+        <v>34389</v>
       </c>
       <c r="D33">
-        <v>54016</v>
+        <v>54246</v>
       </c>
       <c r="E33">
-        <v>68894</v>
+        <v>69059</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -929,16 +929,16 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>35315</v>
+        <v>35352</v>
       </c>
       <c r="C34">
-        <v>49332</v>
+        <v>49383</v>
       </c>
       <c r="D34">
-        <v>70205</v>
+        <v>70234</v>
       </c>
       <c r="E34">
-        <v>83368</v>
+        <v>83381</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -946,13 +946,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>34223</v>
+        <v>34246</v>
       </c>
       <c r="C35">
-        <v>48299</v>
+        <v>48330</v>
       </c>
       <c r="D35">
-        <v>68749</v>
+        <v>68777</v>
       </c>
       <c r="E35">
         <v>82711</v>
@@ -963,16 +963,16 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>22028</v>
+        <v>22064</v>
       </c>
       <c r="C36">
-        <v>34535</v>
+        <v>34565</v>
       </c>
       <c r="D36">
-        <v>56639</v>
+        <v>56690</v>
       </c>
       <c r="E36">
-        <v>72062</v>
+        <v>72110</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -980,16 +980,16 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>22800</v>
+        <v>22837</v>
       </c>
       <c r="C37">
-        <v>33905</v>
+        <v>33995</v>
       </c>
       <c r="D37">
-        <v>53392</v>
+        <v>53575</v>
       </c>
       <c r="E37">
-        <v>68116</v>
+        <v>68272</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -997,16 +997,16 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>22800</v>
+        <v>22837</v>
       </c>
       <c r="C38">
-        <v>33905</v>
+        <v>33995</v>
       </c>
       <c r="D38">
-        <v>53392</v>
+        <v>53575</v>
       </c>
       <c r="E38">
-        <v>68116</v>
+        <v>68272</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -1014,16 +1014,16 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>29311</v>
+        <v>29423</v>
       </c>
       <c r="C39">
-        <v>41965</v>
+        <v>42141</v>
       </c>
       <c r="D39">
-        <v>62465</v>
+        <v>62586</v>
       </c>
       <c r="E39">
-        <v>76546</v>
+        <v>76596</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -1031,16 +1031,16 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>35309</v>
+        <v>35329</v>
       </c>
       <c r="C40">
-        <v>49662</v>
+        <v>49691</v>
       </c>
       <c r="D40">
-        <v>70674</v>
+        <v>70705</v>
       </c>
       <c r="E40">
-        <v>83556</v>
+        <v>83571</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -1048,13 +1048,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>34223</v>
+        <v>34246</v>
       </c>
       <c r="C41">
-        <v>48299</v>
+        <v>48330</v>
       </c>
       <c r="D41">
-        <v>68749</v>
+        <v>68777</v>
       </c>
       <c r="E41">
         <v>82711</v>
@@ -1065,16 +1065,16 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>24410</v>
+        <v>24415</v>
       </c>
       <c r="C42">
-        <v>36560</v>
+        <v>36587</v>
       </c>
       <c r="D42">
-        <v>57603</v>
+        <v>57675</v>
       </c>
       <c r="E42">
-        <v>72257</v>
+        <v>72313</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -1082,13 +1082,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>29492</v>
+        <v>29494</v>
       </c>
       <c r="C43">
-        <v>43119</v>
+        <v>43124</v>
       </c>
       <c r="D43">
-        <v>64051</v>
+        <v>64069</v>
       </c>
       <c r="E43">
         <v>78969</v>
@@ -1099,16 +1099,16 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>28867</v>
+        <v>28879</v>
       </c>
       <c r="C44">
-        <v>43839</v>
+        <v>43852</v>
       </c>
       <c r="D44">
-        <v>66230</v>
+        <v>66263</v>
       </c>
       <c r="E44">
-        <v>80303</v>
+        <v>80324</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -1116,16 +1116,16 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>21139</v>
+        <v>21149</v>
       </c>
       <c r="C45">
-        <v>32972</v>
+        <v>33001</v>
       </c>
       <c r="D45">
-        <v>54766</v>
+        <v>54828</v>
       </c>
       <c r="E45">
-        <v>70066</v>
+        <v>70112</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -1133,16 +1133,16 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>26699</v>
+        <v>26726</v>
       </c>
       <c r="C46">
-        <v>39105</v>
+        <v>39155</v>
       </c>
       <c r="D46">
-        <v>59676</v>
+        <v>59764</v>
       </c>
       <c r="E46">
-        <v>73950</v>
+        <v>74004</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -1150,16 +1150,16 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>27475</v>
+        <v>27477</v>
       </c>
       <c r="C47">
-        <v>42294</v>
+        <v>42298</v>
       </c>
       <c r="D47">
-        <v>65000</v>
+        <v>65013</v>
       </c>
       <c r="E47">
-        <v>79661</v>
+        <v>79676</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -1167,13 +1167,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>25923</v>
+        <v>25924</v>
       </c>
       <c r="C48">
-        <v>39640</v>
+        <v>39644</v>
       </c>
       <c r="D48">
-        <v>61568</v>
+        <v>61580</v>
       </c>
       <c r="E48">
         <v>77171</v>
@@ -1184,16 +1184,16 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>12285</v>
+        <v>12328</v>
       </c>
       <c r="C49">
-        <v>18842</v>
+        <v>18914</v>
       </c>
       <c r="D49">
-        <v>37905</v>
+        <v>37948</v>
       </c>
       <c r="E49">
-        <v>54535</v>
+        <v>54558</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -1201,13 +1201,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>14046</v>
+        <v>14052</v>
       </c>
       <c r="C50">
-        <v>20968</v>
+        <v>20971</v>
       </c>
       <c r="D50">
-        <v>41796</v>
+        <v>41799</v>
       </c>
       <c r="E50">
         <v>61525</v>
@@ -1218,13 +1218,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>12115</v>
+        <v>12116</v>
       </c>
       <c r="C51">
-        <v>18901</v>
+        <v>18905</v>
       </c>
       <c r="D51">
-        <v>38714</v>
+        <v>38719</v>
       </c>
       <c r="E51">
         <v>57085</v>
@@ -1235,13 +1235,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>12776</v>
+        <v>12783</v>
       </c>
       <c r="C52">
-        <v>20232</v>
+        <v>20244</v>
       </c>
       <c r="D52">
-        <v>41499</v>
+        <v>41506</v>
       </c>
       <c r="E52">
         <v>60496</v>
@@ -1252,16 +1252,16 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>10369</v>
+        <v>10381</v>
       </c>
       <c r="C53">
-        <v>16205</v>
+        <v>16226</v>
       </c>
       <c r="D53">
-        <v>33873</v>
+        <v>33909</v>
       </c>
       <c r="E53">
-        <v>49790</v>
+        <v>49809</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -1269,16 +1269,16 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>9742</v>
+        <v>9751</v>
       </c>
       <c r="C54">
-        <v>15440</v>
+        <v>15465</v>
       </c>
       <c r="D54">
-        <v>32744</v>
+        <v>32781</v>
       </c>
       <c r="E54">
-        <v>48206</v>
+        <v>48227</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -1286,13 +1286,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>14046</v>
+        <v>14052</v>
       </c>
       <c r="C55">
-        <v>20968</v>
+        <v>20971</v>
       </c>
       <c r="D55">
-        <v>41796</v>
+        <v>41799</v>
       </c>
       <c r="E55">
         <v>61525</v>
@@ -1303,13 +1303,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>15767</v>
+        <v>15796</v>
       </c>
       <c r="C56">
-        <v>24928</v>
+        <v>24950</v>
       </c>
       <c r="D56">
-        <v>48420</v>
+        <v>48426</v>
       </c>
       <c r="E56">
         <v>67489</v>
@@ -1320,16 +1320,16 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>12054</v>
+        <v>12060</v>
       </c>
       <c r="C57">
-        <v>19102</v>
+        <v>19106</v>
       </c>
       <c r="D57">
-        <v>40560</v>
+        <v>40566</v>
       </c>
       <c r="E57">
-        <v>59930</v>
+        <v>59935</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -1337,16 +1337,16 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>13820</v>
+        <v>13824</v>
       </c>
       <c r="C58">
-        <v>22425</v>
+        <v>22430</v>
       </c>
       <c r="D58">
-        <v>47614</v>
+        <v>47621</v>
       </c>
       <c r="E58">
-        <v>68111</v>
+        <v>68120</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -1354,16 +1354,16 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>13820</v>
+        <v>13824</v>
       </c>
       <c r="C59">
-        <v>22425</v>
+        <v>22430</v>
       </c>
       <c r="D59">
-        <v>47614</v>
+        <v>47621</v>
       </c>
       <c r="E59">
-        <v>68111</v>
+        <v>68120</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -1371,16 +1371,16 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>8753</v>
+        <v>8756</v>
       </c>
       <c r="C60">
-        <v>15224</v>
+        <v>15225</v>
       </c>
       <c r="D60">
-        <v>36771</v>
+        <v>36773</v>
       </c>
       <c r="E60">
-        <v>56555</v>
+        <v>56560</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -1388,16 +1388,16 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>8753</v>
+        <v>8756</v>
       </c>
       <c r="C61">
-        <v>15224</v>
+        <v>15225</v>
       </c>
       <c r="D61">
-        <v>36771</v>
+        <v>36773</v>
       </c>
       <c r="E61">
-        <v>56555</v>
+        <v>56560</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -1405,16 +1405,16 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>5065</v>
+        <v>5080</v>
       </c>
       <c r="C62">
-        <v>10701</v>
+        <v>10708</v>
       </c>
       <c r="D62">
-        <v>32125</v>
+        <v>32129</v>
       </c>
       <c r="E62">
-        <v>52910</v>
+        <v>52915</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -1422,16 +1422,16 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>5065</v>
+        <v>5080</v>
       </c>
       <c r="C63">
-        <v>10701</v>
+        <v>10708</v>
       </c>
       <c r="D63">
-        <v>32125</v>
+        <v>32129</v>
       </c>
       <c r="E63">
-        <v>52910</v>
+        <v>52915</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -1439,16 +1439,16 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>4044</v>
+        <v>4054</v>
       </c>
       <c r="C64">
-        <v>9412</v>
+        <v>9417</v>
       </c>
       <c r="D64">
-        <v>30203</v>
+        <v>30206</v>
       </c>
       <c r="E64">
-        <v>50501</v>
+        <v>50504</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -1456,16 +1456,16 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>4044</v>
+        <v>4054</v>
       </c>
       <c r="C65">
-        <v>9412</v>
+        <v>9417</v>
       </c>
       <c r="D65">
-        <v>30203</v>
+        <v>30206</v>
       </c>
       <c r="E65">
-        <v>50501</v>
+        <v>50504</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -1473,16 +1473,16 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>16277</v>
+        <v>16327</v>
       </c>
       <c r="C66">
-        <v>28961</v>
+        <v>29008</v>
       </c>
       <c r="D66">
-        <v>53561</v>
+        <v>53625</v>
       </c>
       <c r="E66">
-        <v>69988</v>
+        <v>70047</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -1490,13 +1490,13 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="C67">
-        <v>36437</v>
+        <v>36442</v>
       </c>
       <c r="D67">
-        <v>61247</v>
+        <v>61255</v>
       </c>
       <c r="E67">
         <v>77471</v>
@@ -1507,16 +1507,16 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>16277</v>
+        <v>16327</v>
       </c>
       <c r="C68">
-        <v>28961</v>
+        <v>29008</v>
       </c>
       <c r="D68">
-        <v>53561</v>
+        <v>53625</v>
       </c>
       <c r="E68">
-        <v>69988</v>
+        <v>70047</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -1524,13 +1524,13 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="C69">
-        <v>36437</v>
+        <v>36442</v>
       </c>
       <c r="D69">
-        <v>61247</v>
+        <v>61255</v>
       </c>
       <c r="E69">
         <v>77471</v>
@@ -1541,13 +1541,13 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="C70">
-        <v>36437</v>
+        <v>36442</v>
       </c>
       <c r="D70">
-        <v>61247</v>
+        <v>61255</v>
       </c>
       <c r="E70">
         <v>77471</v>
@@ -1558,16 +1558,16 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>24667</v>
+        <v>24672</v>
       </c>
       <c r="C71">
-        <v>41178</v>
+        <v>41183</v>
       </c>
       <c r="D71">
-        <v>65972</v>
+        <v>65983</v>
       </c>
       <c r="E71">
-        <v>80462</v>
+        <v>80478</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -1575,16 +1575,16 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>22265</v>
+        <v>22269</v>
       </c>
       <c r="C72">
-        <v>38076</v>
+        <v>38080</v>
       </c>
       <c r="D72">
-        <v>63276</v>
+        <v>63285</v>
       </c>
       <c r="E72">
-        <v>78376</v>
+        <v>78393</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -1592,16 +1592,16 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>22265</v>
+        <v>22269</v>
       </c>
       <c r="C73">
-        <v>38076</v>
+        <v>38080</v>
       </c>
       <c r="D73">
-        <v>63276</v>
+        <v>63285</v>
       </c>
       <c r="E73">
-        <v>78376</v>
+        <v>78393</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -1609,16 +1609,16 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>22265</v>
+        <v>22269</v>
       </c>
       <c r="C74">
-        <v>38076</v>
+        <v>38080</v>
       </c>
       <c r="D74">
-        <v>63276</v>
+        <v>63285</v>
       </c>
       <c r="E74">
-        <v>78376</v>
+        <v>78393</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -1626,16 +1626,16 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>14556</v>
+        <v>14557</v>
       </c>
       <c r="C75">
-        <v>27320</v>
+        <v>27322</v>
       </c>
       <c r="D75">
-        <v>53452</v>
+        <v>53455</v>
       </c>
       <c r="E75">
-        <v>70617</v>
+        <v>70628</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -1643,13 +1643,13 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>21092</v>
+        <v>21098</v>
       </c>
       <c r="C76">
-        <v>36437</v>
+        <v>36442</v>
       </c>
       <c r="D76">
-        <v>61247</v>
+        <v>61255</v>
       </c>
       <c r="E76">
         <v>77471</v>
@@ -1660,16 +1660,16 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="C77">
-        <v>35705</v>
+        <v>35709</v>
       </c>
       <c r="D77">
-        <v>61620</v>
+        <v>61629</v>
       </c>
       <c r="E77">
-        <v>77282</v>
+        <v>77302</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -1677,16 +1677,16 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="C78">
-        <v>35705</v>
+        <v>35709</v>
       </c>
       <c r="D78">
-        <v>61620</v>
+        <v>61629</v>
       </c>
       <c r="E78">
-        <v>77282</v>
+        <v>77302</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -1694,16 +1694,16 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="C79">
-        <v>35705</v>
+        <v>35709</v>
       </c>
       <c r="D79">
-        <v>61620</v>
+        <v>61629</v>
       </c>
       <c r="E79">
-        <v>77282</v>
+        <v>77302</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -1711,16 +1711,16 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>20189</v>
+        <v>20196</v>
       </c>
       <c r="C80">
-        <v>35705</v>
+        <v>35709</v>
       </c>
       <c r="D80">
-        <v>61620</v>
+        <v>61629</v>
       </c>
       <c r="E80">
-        <v>77282</v>
+        <v>77302</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -1728,16 +1728,16 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>28268</v>
+        <v>28272</v>
       </c>
       <c r="C81">
-        <v>43674</v>
+        <v>43678</v>
       </c>
       <c r="D81">
-        <v>66132</v>
+        <v>66144</v>
       </c>
       <c r="E81">
-        <v>79855</v>
+        <v>79870</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -1745,16 +1745,16 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>28268</v>
+        <v>28272</v>
       </c>
       <c r="C82">
-        <v>43674</v>
+        <v>43678</v>
       </c>
       <c r="D82">
-        <v>66132</v>
+        <v>66144</v>
       </c>
       <c r="E82">
-        <v>79855</v>
+        <v>79870</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -1762,16 +1762,16 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>18733</v>
+        <v>18736</v>
       </c>
       <c r="C83">
-        <v>33448</v>
+        <v>33451</v>
       </c>
       <c r="D83">
-        <v>57894</v>
+        <v>57906</v>
       </c>
       <c r="E83">
-        <v>72628</v>
+        <v>72647</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -1779,16 +1779,16 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>18733</v>
+        <v>18736</v>
       </c>
       <c r="C84">
-        <v>33448</v>
+        <v>33451</v>
       </c>
       <c r="D84">
-        <v>57894</v>
+        <v>57906</v>
       </c>
       <c r="E84">
-        <v>72628</v>
+        <v>72647</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -1796,16 +1796,16 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>28697</v>
+        <v>28706</v>
       </c>
       <c r="C85">
-        <v>45212</v>
+        <v>45238</v>
       </c>
       <c r="D85">
-        <v>67169</v>
+        <v>67205</v>
       </c>
       <c r="E85">
-        <v>79600</v>
+        <v>79623</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -1813,16 +1813,16 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>28697</v>
+        <v>28706</v>
       </c>
       <c r="C86">
-        <v>45212</v>
+        <v>45238</v>
       </c>
       <c r="D86">
-        <v>67169</v>
+        <v>67205</v>
       </c>
       <c r="E86">
-        <v>79600</v>
+        <v>79623</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -1830,16 +1830,16 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>27930</v>
+        <v>27947</v>
       </c>
       <c r="C87">
-        <v>45223</v>
+        <v>45249</v>
       </c>
       <c r="D87">
-        <v>68033</v>
+        <v>68069</v>
       </c>
       <c r="E87">
-        <v>80642</v>
+        <v>80664</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -1847,16 +1847,16 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>27930</v>
+        <v>27947</v>
       </c>
       <c r="C88">
-        <v>45223</v>
+        <v>45249</v>
       </c>
       <c r="D88">
-        <v>68033</v>
+        <v>68069</v>
       </c>
       <c r="E88">
-        <v>80642</v>
+        <v>80664</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -1864,16 +1864,16 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>27930</v>
+        <v>27947</v>
       </c>
       <c r="C89">
-        <v>45223</v>
+        <v>45249</v>
       </c>
       <c r="D89">
-        <v>68033</v>
+        <v>68069</v>
       </c>
       <c r="E89">
-        <v>80642</v>
+        <v>80664</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -1881,16 +1881,16 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>45279</v>
+        <v>45420</v>
       </c>
       <c r="C90">
-        <v>54182</v>
+        <v>54404</v>
       </c>
       <c r="D90">
-        <v>67925</v>
+        <v>68534</v>
       </c>
       <c r="E90">
-        <v>77359</v>
+        <v>78272</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -1898,16 +1898,16 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>45245</v>
+        <v>45388</v>
       </c>
       <c r="C91">
-        <v>54087</v>
+        <v>54317</v>
       </c>
       <c r="D91">
-        <v>67730</v>
+        <v>68378</v>
       </c>
       <c r="E91">
-        <v>76975</v>
+        <v>77983</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -1915,16 +1915,16 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>45099</v>
+        <v>45251</v>
       </c>
       <c r="C92">
-        <v>53680</v>
+        <v>53944</v>
       </c>
       <c r="D92">
-        <v>66897</v>
+        <v>67710</v>
       </c>
       <c r="E92">
-        <v>75331</v>
+        <v>76748</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -1932,16 +1932,16 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>45544</v>
+        <v>45668</v>
       </c>
       <c r="C93">
-        <v>54919</v>
+        <v>55078</v>
       </c>
       <c r="D93">
-        <v>69432</v>
+        <v>69742</v>
       </c>
       <c r="E93">
-        <v>80333</v>
+        <v>80507</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -1949,16 +1949,16 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>41252</v>
+        <v>41444</v>
       </c>
       <c r="C94">
-        <v>50061</v>
+        <v>50370</v>
       </c>
       <c r="D94">
-        <v>59827</v>
+        <v>60933</v>
       </c>
       <c r="E94">
-        <v>68816</v>
+        <v>71116</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -1966,16 +1966,16 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>45519</v>
+        <v>45645</v>
       </c>
       <c r="C95">
-        <v>54852</v>
+        <v>55017</v>
       </c>
       <c r="D95">
-        <v>69294</v>
+        <v>69632</v>
       </c>
       <c r="E95">
-        <v>80062</v>
+        <v>80303</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -1983,16 +1983,16 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>45148</v>
+        <v>45297</v>
       </c>
       <c r="C96">
-        <v>53818</v>
+        <v>54070</v>
       </c>
       <c r="D96">
-        <v>67180</v>
+        <v>67937</v>
       </c>
       <c r="E96">
-        <v>75889</v>
+        <v>77167</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -2000,16 +2000,16 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>45544</v>
+        <v>45668</v>
       </c>
       <c r="C97">
-        <v>54919</v>
+        <v>55078</v>
       </c>
       <c r="D97">
-        <v>69432</v>
+        <v>69742</v>
       </c>
       <c r="E97">
-        <v>80333</v>
+        <v>80507</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -2017,16 +2017,16 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>40967</v>
+        <v>41110</v>
       </c>
       <c r="C98">
-        <v>50936</v>
+        <v>51102</v>
       </c>
       <c r="D98">
-        <v>66777</v>
+        <v>67253</v>
       </c>
       <c r="E98">
-        <v>78995</v>
+        <v>79293</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -2034,16 +2034,16 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>40808</v>
+        <v>40959</v>
       </c>
       <c r="C99">
-        <v>50472</v>
+        <v>50665</v>
       </c>
       <c r="D99">
-        <v>65781</v>
+        <v>66443</v>
       </c>
       <c r="E99">
-        <v>77287</v>
+        <v>78066</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -2051,16 +2051,16 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>40759</v>
+        <v>40924</v>
       </c>
       <c r="C100">
-        <v>50111</v>
+        <v>50358</v>
       </c>
       <c r="D100">
-        <v>65077</v>
+        <v>65554</v>
       </c>
       <c r="E100">
-        <v>76567</v>
+        <v>77032</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -2068,16 +2068,16 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>40656</v>
+        <v>40827</v>
       </c>
       <c r="C101">
-        <v>49838</v>
+        <v>50110</v>
       </c>
       <c r="D101">
-        <v>64489</v>
+        <v>65072</v>
       </c>
       <c r="E101">
-        <v>75502</v>
+        <v>76234</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -2085,16 +2085,16 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>40856</v>
+        <v>41015</v>
       </c>
       <c r="C102">
-        <v>50366</v>
+        <v>50589</v>
       </c>
       <c r="D102">
-        <v>65623</v>
+        <v>66003</v>
       </c>
       <c r="E102">
-        <v>77557</v>
+        <v>77774</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -2102,16 +2102,16 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>36090</v>
+        <v>36312</v>
       </c>
       <c r="C103">
-        <v>46777</v>
+        <v>47111</v>
       </c>
       <c r="D103">
-        <v>63852</v>
+        <v>64614</v>
       </c>
       <c r="E103">
-        <v>77381</v>
+        <v>77761</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -2119,16 +2119,16 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>36090</v>
+        <v>36312</v>
       </c>
       <c r="C104">
-        <v>46777</v>
+        <v>47111</v>
       </c>
       <c r="D104">
-        <v>63852</v>
+        <v>64614</v>
       </c>
       <c r="E104">
-        <v>77381</v>
+        <v>77761</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -2136,16 +2136,16 @@
         <v>104</v>
       </c>
       <c r="B105">
-        <v>38301</v>
+        <v>38390</v>
       </c>
       <c r="C105">
-        <v>51131</v>
+        <v>51235</v>
       </c>
       <c r="D105">
-        <v>69526</v>
+        <v>69709</v>
       </c>
       <c r="E105">
-        <v>81827</v>
+        <v>81961</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -2153,16 +2153,16 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>42407</v>
+        <v>42522</v>
       </c>
       <c r="C106">
-        <v>56826</v>
+        <v>56951</v>
       </c>
       <c r="D106">
-        <v>75633</v>
+        <v>75734</v>
       </c>
       <c r="E106">
-        <v>86331</v>
+        <v>86376</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -2170,16 +2170,16 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>42407</v>
+        <v>42522</v>
       </c>
       <c r="C107">
-        <v>56826</v>
+        <v>56951</v>
       </c>
       <c r="D107">
-        <v>75633</v>
+        <v>75734</v>
       </c>
       <c r="E107">
-        <v>86331</v>
+        <v>86376</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -2187,13 +2187,13 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>48128</v>
+        <v>48147</v>
       </c>
       <c r="C108">
-        <v>63101</v>
+        <v>63112</v>
       </c>
       <c r="D108">
-        <v>80235</v>
+        <v>80245</v>
       </c>
       <c r="E108">
         <v>90420</v>
@@ -2204,16 +2204,16 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>35052</v>
+        <v>35358</v>
       </c>
       <c r="C109">
-        <v>48776</v>
+        <v>49159</v>
       </c>
       <c r="D109">
-        <v>67810</v>
+        <v>68086</v>
       </c>
       <c r="E109">
-        <v>80409</v>
+        <v>80561</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -2221,16 +2221,16 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>35052</v>
+        <v>35358</v>
       </c>
       <c r="C110">
-        <v>48776</v>
+        <v>49159</v>
       </c>
       <c r="D110">
-        <v>67810</v>
+        <v>68086</v>
       </c>
       <c r="E110">
-        <v>80409</v>
+        <v>80561</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -2238,16 +2238,16 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>34512</v>
+        <v>34840</v>
       </c>
       <c r="C111">
-        <v>47756</v>
+        <v>48221</v>
       </c>
       <c r="D111">
-        <v>66076</v>
+        <v>66560</v>
       </c>
       <c r="E111">
-        <v>78519</v>
+        <v>79036</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -2255,16 +2255,16 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>35007</v>
+        <v>35554</v>
       </c>
       <c r="C112">
-        <v>46399</v>
+        <v>47151</v>
       </c>
       <c r="D112">
-        <v>63904</v>
+        <v>64891</v>
       </c>
       <c r="E112">
-        <v>77593</v>
+        <v>77991</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -2272,16 +2272,16 @@
         <v>112</v>
       </c>
       <c r="B113">
-        <v>32777</v>
+        <v>33099</v>
       </c>
       <c r="C113">
-        <v>46726</v>
+        <v>47105</v>
       </c>
       <c r="D113">
-        <v>66432</v>
+        <v>66749</v>
       </c>
       <c r="E113">
-        <v>79411</v>
+        <v>79602</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -2289,16 +2289,16 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>38037</v>
+        <v>38226</v>
       </c>
       <c r="C114">
-        <v>53009</v>
+        <v>53194</v>
       </c>
       <c r="D114">
-        <v>72860</v>
+        <v>72977</v>
       </c>
       <c r="E114">
-        <v>84233</v>
+        <v>84282</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -2306,16 +2306,16 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>34922</v>
+        <v>35477</v>
       </c>
       <c r="C115">
-        <v>46192</v>
+        <v>46974</v>
       </c>
       <c r="D115">
-        <v>63527</v>
+        <v>64609</v>
       </c>
       <c r="E115">
-        <v>77043</v>
+        <v>77612</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -2323,16 +2323,16 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>35007</v>
+        <v>35554</v>
       </c>
       <c r="C116">
-        <v>46399</v>
+        <v>47151</v>
       </c>
       <c r="D116">
-        <v>63904</v>
+        <v>64891</v>
       </c>
       <c r="E116">
-        <v>77593</v>
+        <v>77991</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -2340,16 +2340,16 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>32810</v>
+        <v>33130</v>
       </c>
       <c r="C117">
-        <v>46789</v>
+        <v>47163</v>
       </c>
       <c r="D117">
-        <v>66540</v>
+        <v>66843</v>
       </c>
       <c r="E117">
-        <v>79528</v>
+        <v>79696</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -2357,16 +2357,16 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>45520</v>
+        <v>45572</v>
       </c>
       <c r="C118">
-        <v>61878</v>
+        <v>61913</v>
       </c>
       <c r="D118">
-        <v>80621</v>
+        <v>80638</v>
       </c>
       <c r="E118">
-        <v>89947</v>
+        <v>89956</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -2374,13 +2374,13 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>40639</v>
+        <v>40669</v>
       </c>
       <c r="C119">
-        <v>56597</v>
+        <v>56632</v>
       </c>
       <c r="D119">
-        <v>75773</v>
+        <v>75789</v>
       </c>
       <c r="E119">
         <v>87243</v>
@@ -2391,16 +2391,16 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>42587</v>
+        <v>42686</v>
       </c>
       <c r="C120">
-        <v>52394</v>
+        <v>52526</v>
       </c>
       <c r="D120">
-        <v>67714</v>
+        <v>68096</v>
       </c>
       <c r="E120">
-        <v>79340</v>
+        <v>79569</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -2408,16 +2408,16 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>42587</v>
+        <v>42686</v>
       </c>
       <c r="C121">
-        <v>52394</v>
+        <v>52526</v>
       </c>
       <c r="D121">
-        <v>67714</v>
+        <v>68096</v>
       </c>
       <c r="E121">
-        <v>79340</v>
+        <v>79569</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -2425,16 +2425,16 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>36357</v>
+        <v>36595</v>
       </c>
       <c r="C122">
-        <v>49979</v>
+        <v>50276</v>
       </c>
       <c r="D122">
-        <v>68362</v>
+        <v>68667</v>
       </c>
       <c r="E122">
-        <v>80608</v>
+        <v>80759</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -2442,16 +2442,16 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>36155</v>
+        <v>36399</v>
       </c>
       <c r="C123">
-        <v>49608</v>
+        <v>49929</v>
       </c>
       <c r="D123">
-        <v>67739</v>
+        <v>68128</v>
       </c>
       <c r="E123">
-        <v>79942</v>
+        <v>80227</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -2459,16 +2459,16 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>36357</v>
+        <v>36595</v>
       </c>
       <c r="C124">
-        <v>49979</v>
+        <v>50276</v>
       </c>
       <c r="D124">
-        <v>68362</v>
+        <v>68667</v>
       </c>
       <c r="E124">
-        <v>80608</v>
+        <v>80759</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -2476,16 +2476,16 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>35238</v>
+        <v>35335</v>
       </c>
       <c r="C125">
-        <v>48909</v>
+        <v>49184</v>
       </c>
       <c r="D125">
-        <v>67473</v>
+        <v>67779</v>
       </c>
       <c r="E125">
-        <v>79801</v>
+        <v>79954</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -2493,16 +2493,16 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>40448</v>
+        <v>40517</v>
       </c>
       <c r="C126">
-        <v>54816</v>
+        <v>54970</v>
       </c>
       <c r="D126">
-        <v>73380</v>
+        <v>73500</v>
       </c>
       <c r="E126">
-        <v>84312</v>
+        <v>84355</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -2510,16 +2510,16 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>42938</v>
+        <v>43148</v>
       </c>
       <c r="C127">
-        <v>57244</v>
+        <v>57458</v>
       </c>
       <c r="D127">
-        <v>75201</v>
+        <v>75335</v>
       </c>
       <c r="E127">
-        <v>85698</v>
+        <v>85749</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -2527,13 +2527,13 @@
         <v>127</v>
       </c>
       <c r="B128">
-        <v>48414</v>
+        <v>48465</v>
       </c>
       <c r="C128">
-        <v>62307</v>
+        <v>62336</v>
       </c>
       <c r="D128">
-        <v>78490</v>
+        <v>78505</v>
       </c>
       <c r="E128">
         <v>88953</v>
@@ -2544,13 +2544,13 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>48414</v>
+        <v>48465</v>
       </c>
       <c r="C129">
-        <v>62307</v>
+        <v>62336</v>
       </c>
       <c r="D129">
-        <v>78490</v>
+        <v>78505</v>
       </c>
       <c r="E129">
         <v>88953</v>
@@ -2561,16 +2561,16 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>44375</v>
+        <v>44534</v>
       </c>
       <c r="C130">
-        <v>53342</v>
+        <v>53554</v>
       </c>
       <c r="D130">
-        <v>67625</v>
+        <v>68003</v>
       </c>
       <c r="E130">
-        <v>78633</v>
+        <v>78909</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -2578,16 +2578,16 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>44025</v>
+        <v>44210</v>
       </c>
       <c r="C131">
-        <v>52382</v>
+        <v>52690</v>
       </c>
       <c r="D131">
-        <v>65592</v>
+        <v>66367</v>
       </c>
       <c r="E131">
-        <v>74692</v>
+        <v>75943</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -2595,16 +2595,16 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>44051</v>
+        <v>44234</v>
       </c>
       <c r="C132">
-        <v>52454</v>
+        <v>52755</v>
       </c>
       <c r="D132">
-        <v>65744</v>
+        <v>66489</v>
       </c>
       <c r="E132">
-        <v>74986</v>
+        <v>76164</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -2612,16 +2612,16 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>44176</v>
+        <v>44349</v>
       </c>
       <c r="C133">
-        <v>52795</v>
+        <v>53062</v>
       </c>
       <c r="D133">
-        <v>66466</v>
+        <v>67070</v>
       </c>
       <c r="E133">
-        <v>76386</v>
+        <v>77218</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -2629,16 +2629,16 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>44542</v>
+        <v>44689</v>
       </c>
       <c r="C134">
-        <v>53281</v>
+        <v>53477</v>
       </c>
       <c r="D134">
-        <v>66677</v>
+        <v>67343</v>
       </c>
       <c r="E134">
-        <v>75641</v>
+        <v>76781</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -2646,16 +2646,16 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>42452</v>
+        <v>42682</v>
       </c>
       <c r="C135">
-        <v>51425</v>
+        <v>51699</v>
       </c>
       <c r="D135">
-        <v>65899</v>
+        <v>66343</v>
       </c>
       <c r="E135">
-        <v>77330</v>
+        <v>77674</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -2663,16 +2663,16 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>39958</v>
+        <v>40298</v>
       </c>
       <c r="C136">
-        <v>48864</v>
+        <v>49303</v>
       </c>
       <c r="D136">
-        <v>63501</v>
+        <v>64188</v>
       </c>
       <c r="E136">
-        <v>75335</v>
+        <v>75890</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -2680,16 +2680,16 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>40060</v>
+        <v>40391</v>
       </c>
       <c r="C137">
-        <v>49122</v>
+        <v>49527</v>
       </c>
       <c r="D137">
-        <v>64049</v>
+        <v>64618</v>
       </c>
       <c r="E137">
-        <v>76280</v>
+        <v>76570</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -2697,16 +2697,16 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>40060</v>
+        <v>40391</v>
       </c>
       <c r="C138">
-        <v>49122</v>
+        <v>49527</v>
       </c>
       <c r="D138">
-        <v>64049</v>
+        <v>64618</v>
       </c>
       <c r="E138">
-        <v>76280</v>
+        <v>76570</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -2714,16 +2714,16 @@
         <v>138</v>
       </c>
       <c r="B139">
-        <v>40999</v>
+        <v>41198</v>
       </c>
       <c r="C139">
-        <v>50476</v>
+        <v>50746</v>
       </c>
       <c r="D139">
-        <v>65602</v>
+        <v>66065</v>
       </c>
       <c r="E139">
-        <v>77525</v>
+        <v>77779</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -2731,16 +2731,16 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>39925</v>
+        <v>40065</v>
       </c>
       <c r="C140">
-        <v>50294</v>
+        <v>50424</v>
       </c>
       <c r="D140">
-        <v>60187</v>
+        <v>60311</v>
       </c>
       <c r="E140">
-        <v>72031</v>
+        <v>72037</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -2748,16 +2748,16 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>40999</v>
+        <v>41198</v>
       </c>
       <c r="C141">
-        <v>50476</v>
+        <v>50746</v>
       </c>
       <c r="D141">
-        <v>65602</v>
+        <v>66065</v>
       </c>
       <c r="E141">
-        <v>77525</v>
+        <v>77779</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -2765,16 +2765,16 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>40962</v>
+        <v>41164</v>
       </c>
       <c r="C142">
-        <v>50376</v>
+        <v>50655</v>
       </c>
       <c r="D142">
-        <v>65388</v>
+        <v>65895</v>
       </c>
       <c r="E142">
-        <v>77146</v>
+        <v>77504</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -2782,16 +2782,16 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>36315</v>
+        <v>36674</v>
       </c>
       <c r="C143">
-        <v>47447</v>
+        <v>47968</v>
       </c>
       <c r="D143">
-        <v>62025</v>
+        <v>63030</v>
       </c>
       <c r="E143">
-        <v>73177</v>
+        <v>74651</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -2799,16 +2799,16 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>38351</v>
+        <v>38627</v>
       </c>
       <c r="C144">
-        <v>51062</v>
+        <v>51337</v>
       </c>
       <c r="D144">
-        <v>68280</v>
+        <v>68521</v>
       </c>
       <c r="E144">
-        <v>80127</v>
+        <v>80259</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -2816,16 +2816,16 @@
         <v>144</v>
       </c>
       <c r="B145">
-        <v>38351</v>
+        <v>38627</v>
       </c>
       <c r="C145">
-        <v>51062</v>
+        <v>51337</v>
       </c>
       <c r="D145">
-        <v>68280</v>
+        <v>68521</v>
       </c>
       <c r="E145">
-        <v>80127</v>
+        <v>80259</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -2833,16 +2833,16 @@
         <v>145</v>
       </c>
       <c r="B146">
-        <v>47497</v>
+        <v>47553</v>
       </c>
       <c r="C146">
-        <v>60994</v>
+        <v>61032</v>
       </c>
       <c r="D146">
-        <v>76182</v>
+        <v>76214</v>
       </c>
       <c r="E146">
-        <v>86918</v>
+        <v>86919</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -2850,16 +2850,16 @@
         <v>146</v>
       </c>
       <c r="B147">
-        <v>40936</v>
+        <v>41155</v>
       </c>
       <c r="C147">
-        <v>53167</v>
+        <v>53345</v>
       </c>
       <c r="D147">
-        <v>70807</v>
+        <v>70893</v>
       </c>
       <c r="E147">
-        <v>82223</v>
+        <v>82260</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -2867,16 +2867,16 @@
         <v>147</v>
       </c>
       <c r="B148">
-        <v>36986</v>
+        <v>37374</v>
       </c>
       <c r="C148">
-        <v>48529</v>
+        <v>48882</v>
       </c>
       <c r="D148">
-        <v>65498</v>
+        <v>65725</v>
       </c>
       <c r="E148">
-        <v>77734</v>
+        <v>77860</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -2884,16 +2884,16 @@
         <v>148</v>
       </c>
       <c r="B149">
-        <v>36082</v>
+        <v>36447</v>
       </c>
       <c r="C149">
-        <v>45335</v>
+        <v>45741</v>
       </c>
       <c r="D149">
-        <v>60573</v>
+        <v>61089</v>
       </c>
       <c r="E149">
-        <v>73102</v>
+        <v>73376</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -2901,16 +2901,16 @@
         <v>149</v>
       </c>
       <c r="B150">
-        <v>36082</v>
+        <v>36447</v>
       </c>
       <c r="C150">
-        <v>45335</v>
+        <v>45741</v>
       </c>
       <c r="D150">
-        <v>60573</v>
+        <v>61089</v>
       </c>
       <c r="E150">
-        <v>73102</v>
+        <v>73376</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -2918,16 +2918,16 @@
         <v>150</v>
       </c>
       <c r="B151">
-        <v>35921</v>
+        <v>36302</v>
       </c>
       <c r="C151">
-        <v>44936</v>
+        <v>45396</v>
       </c>
       <c r="D151">
-        <v>59713</v>
+        <v>60401</v>
       </c>
       <c r="E151">
-        <v>71588</v>
+        <v>72266</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -2935,16 +2935,16 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>36082</v>
+        <v>36447</v>
       </c>
       <c r="C152">
-        <v>45335</v>
+        <v>45741</v>
       </c>
       <c r="D152">
-        <v>60573</v>
+        <v>61089</v>
       </c>
       <c r="E152">
-        <v>73102</v>
+        <v>73376</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -2952,13 +2952,13 @@
         <v>152</v>
       </c>
       <c r="B153">
-        <v>43377</v>
+        <v>43396</v>
       </c>
       <c r="C153">
-        <v>55664</v>
+        <v>55694</v>
       </c>
       <c r="D153">
-        <v>73010</v>
+        <v>73023</v>
       </c>
       <c r="E153">
         <v>85166</v>
@@ -2969,13 +2969,13 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>43377</v>
+        <v>43396</v>
       </c>
       <c r="C154">
-        <v>55664</v>
+        <v>55694</v>
       </c>
       <c r="D154">
-        <v>73010</v>
+        <v>73023</v>
       </c>
       <c r="E154">
         <v>85166</v>
@@ -2986,16 +2986,16 @@
         <v>154</v>
       </c>
       <c r="B155">
-        <v>31416</v>
+        <v>31745</v>
       </c>
       <c r="C155">
-        <v>42564</v>
+        <v>42887</v>
       </c>
       <c r="D155">
-        <v>60045</v>
+        <v>60307</v>
       </c>
       <c r="E155">
-        <v>73056</v>
+        <v>73198</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -3003,16 +3003,16 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>31416</v>
+        <v>31745</v>
       </c>
       <c r="C156">
-        <v>42564</v>
+        <v>42887</v>
       </c>
       <c r="D156">
-        <v>60045</v>
+        <v>60307</v>
       </c>
       <c r="E156">
-        <v>73056</v>
+        <v>73198</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -3020,16 +3020,16 @@
         <v>156</v>
       </c>
       <c r="B157">
-        <v>35522</v>
+        <v>35687</v>
       </c>
       <c r="C157">
-        <v>47320</v>
+        <v>47485</v>
       </c>
       <c r="D157">
-        <v>65634</v>
+        <v>65739</v>
       </c>
       <c r="E157">
-        <v>77996</v>
+        <v>78038</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -3037,16 +3037,16 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>34736</v>
+        <v>34983</v>
       </c>
       <c r="C158">
-        <v>46020</v>
+        <v>46251</v>
       </c>
       <c r="D158">
-        <v>63186</v>
+        <v>63393</v>
       </c>
       <c r="E158">
-        <v>75743</v>
+        <v>75871</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -3054,16 +3054,16 @@
         <v>158</v>
       </c>
       <c r="B159">
-        <v>33850</v>
+        <v>34190</v>
       </c>
       <c r="C159">
-        <v>42847</v>
+        <v>43261</v>
       </c>
       <c r="D159">
-        <v>58075</v>
+        <v>58684</v>
       </c>
       <c r="E159">
-        <v>70923</v>
+        <v>71223</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -3071,16 +3071,16 @@
         <v>159</v>
       </c>
       <c r="B160">
-        <v>31791</v>
+        <v>32019</v>
       </c>
       <c r="C160">
-        <v>43092</v>
+        <v>43318</v>
       </c>
       <c r="D160">
-        <v>60731</v>
+        <v>60947</v>
       </c>
       <c r="E160">
-        <v>73758</v>
+        <v>73898</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -3088,16 +3088,16 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>35830</v>
+        <v>35888</v>
       </c>
       <c r="C161">
-        <v>48311</v>
+        <v>48418</v>
       </c>
       <c r="D161">
-        <v>67248</v>
+        <v>67344</v>
       </c>
       <c r="E161">
-        <v>79677</v>
+        <v>79720</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -3105,13 +3105,13 @@
         <v>161</v>
       </c>
       <c r="B162">
-        <v>40678</v>
+        <v>40706</v>
       </c>
       <c r="C162">
-        <v>53813</v>
+        <v>53835</v>
       </c>
       <c r="D162">
-        <v>71761</v>
+        <v>71778</v>
       </c>
       <c r="E162">
         <v>84242</v>
@@ -3122,16 +3122,16 @@
         <v>162</v>
       </c>
       <c r="B163">
-        <v>33779</v>
+        <v>33895</v>
       </c>
       <c r="C163">
-        <v>43377</v>
+        <v>43694</v>
       </c>
       <c r="D163">
-        <v>59185</v>
+        <v>59856</v>
       </c>
       <c r="E163">
-        <v>72293</v>
+        <v>72614</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -3139,16 +3139,16 @@
         <v>163</v>
       </c>
       <c r="B164">
-        <v>34616</v>
+        <v>34712</v>
       </c>
       <c r="C164">
-        <v>46650</v>
+        <v>46864</v>
       </c>
       <c r="D164">
-        <v>64372</v>
+        <v>64606</v>
       </c>
       <c r="E164">
-        <v>77013</v>
+        <v>77148</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -3156,16 +3156,16 @@
         <v>164</v>
       </c>
       <c r="B165">
-        <v>30607</v>
+        <v>30670</v>
       </c>
       <c r="C165">
-        <v>42695</v>
+        <v>42886</v>
       </c>
       <c r="D165">
-        <v>61076</v>
+        <v>61349</v>
       </c>
       <c r="E165">
-        <v>74229</v>
+        <v>74386</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -3173,16 +3173,16 @@
         <v>165</v>
       </c>
       <c r="B166">
-        <v>30607</v>
+        <v>30670</v>
       </c>
       <c r="C166">
-        <v>42695</v>
+        <v>42886</v>
       </c>
       <c r="D166">
-        <v>61076</v>
+        <v>61349</v>
       </c>
       <c r="E166">
-        <v>74229</v>
+        <v>74386</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -3190,16 +3190,16 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>35666</v>
+        <v>35772</v>
       </c>
       <c r="C167">
-        <v>49024</v>
+        <v>49180</v>
       </c>
       <c r="D167">
-        <v>68457</v>
+        <v>68569</v>
       </c>
       <c r="E167">
-        <v>80873</v>
+        <v>80918</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -3207,16 +3207,16 @@
         <v>167</v>
       </c>
       <c r="B168">
-        <v>41931</v>
+        <v>41962</v>
       </c>
       <c r="C168">
-        <v>56690</v>
+        <v>56720</v>
       </c>
       <c r="D168">
-        <v>75725</v>
+        <v>75743</v>
       </c>
       <c r="E168">
-        <v>86861</v>
+        <v>86870</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -3224,16 +3224,16 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>42796</v>
+        <v>43035</v>
       </c>
       <c r="C169">
-        <v>52422</v>
+        <v>52750</v>
       </c>
       <c r="D169">
-        <v>67419</v>
+        <v>67915</v>
       </c>
       <c r="E169">
-        <v>78941</v>
+        <v>79242</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -3241,16 +3241,16 @@
         <v>169</v>
       </c>
       <c r="B170">
-        <v>42274</v>
+        <v>42455</v>
       </c>
       <c r="C170">
-        <v>51047</v>
+        <v>51321</v>
       </c>
       <c r="D170">
-        <v>65333</v>
+        <v>65834</v>
       </c>
       <c r="E170">
-        <v>76136</v>
+        <v>76778</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -3258,16 +3258,16 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>42825</v>
+        <v>43062</v>
       </c>
       <c r="C171">
-        <v>52494</v>
+        <v>52814</v>
       </c>
       <c r="D171">
-        <v>67557</v>
+        <v>68024</v>
       </c>
       <c r="E171">
-        <v>79181</v>
+        <v>79417</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -3275,16 +3275,16 @@
         <v>171</v>
       </c>
       <c r="B172">
-        <v>42429</v>
+        <v>42598</v>
       </c>
       <c r="C172">
-        <v>51489</v>
+        <v>51717</v>
       </c>
       <c r="D172">
-        <v>66295</v>
+        <v>66632</v>
       </c>
       <c r="E172">
-        <v>77946</v>
+        <v>78150</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -3292,16 +3292,16 @@
         <v>172</v>
       </c>
       <c r="B173">
-        <v>42147</v>
+        <v>42337</v>
       </c>
       <c r="C173">
-        <v>50686</v>
+        <v>50997</v>
       </c>
       <c r="D173">
-        <v>64546</v>
+        <v>65181</v>
       </c>
       <c r="E173">
-        <v>74654</v>
+        <v>75655</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -3309,16 +3309,16 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>42765</v>
+        <v>42865</v>
       </c>
       <c r="C174">
-        <v>50891</v>
+        <v>51067</v>
       </c>
       <c r="D174">
-        <v>64043</v>
+        <v>64680</v>
       </c>
       <c r="E174">
-        <v>73401</v>
+        <v>74618</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -3326,16 +3326,16 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>43064</v>
+        <v>43271</v>
       </c>
       <c r="C175">
-        <v>56178</v>
+        <v>56348</v>
       </c>
       <c r="D175">
-        <v>74195</v>
+        <v>74285</v>
       </c>
       <c r="E175">
-        <v>85165</v>
+        <v>85205</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -3343,16 +3343,16 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>38779</v>
+        <v>39106</v>
       </c>
       <c r="C176">
-        <v>51144</v>
+        <v>51496</v>
       </c>
       <c r="D176">
-        <v>68875</v>
+        <v>69107</v>
       </c>
       <c r="E176">
-        <v>81049</v>
+        <v>81183</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -3360,16 +3360,16 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>38779</v>
+        <v>39106</v>
       </c>
       <c r="C177">
-        <v>51144</v>
+        <v>51496</v>
       </c>
       <c r="D177">
-        <v>68875</v>
+        <v>69107</v>
       </c>
       <c r="E177">
-        <v>81049</v>
+        <v>81183</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -3377,16 +3377,16 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>38572</v>
+        <v>38911</v>
       </c>
       <c r="C178">
-        <v>47915</v>
+        <v>48370</v>
       </c>
       <c r="D178">
-        <v>63399</v>
+        <v>64057</v>
       </c>
       <c r="E178">
-        <v>76162</v>
+        <v>76493</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -3394,16 +3394,16 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>39317</v>
+        <v>39584</v>
       </c>
       <c r="C179">
-        <v>50932</v>
+        <v>51198</v>
       </c>
       <c r="D179">
-        <v>67953</v>
+        <v>68153</v>
       </c>
       <c r="E179">
-        <v>79977</v>
+        <v>80107</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -3411,16 +3411,16 @@
         <v>179</v>
       </c>
       <c r="B180">
-        <v>49056</v>
+        <v>49097</v>
       </c>
       <c r="C180">
-        <v>62908</v>
+        <v>62931</v>
       </c>
       <c r="D180">
-        <v>80025</v>
+        <v>80036</v>
       </c>
       <c r="E180">
-        <v>89545</v>
+        <v>89552</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -3428,16 +3428,16 @@
         <v>180</v>
       </c>
       <c r="B181">
-        <v>49056</v>
+        <v>49097</v>
       </c>
       <c r="C181">
-        <v>62908</v>
+        <v>62931</v>
       </c>
       <c r="D181">
-        <v>80025</v>
+        <v>80036</v>
       </c>
       <c r="E181">
-        <v>89545</v>
+        <v>89552</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -3445,16 +3445,16 @@
         <v>181</v>
       </c>
       <c r="B182">
-        <v>42666</v>
+        <v>42695</v>
       </c>
       <c r="C182">
-        <v>56174</v>
+        <v>56203</v>
       </c>
       <c r="D182">
-        <v>74773</v>
+        <v>74791</v>
       </c>
       <c r="E182">
-        <v>85890</v>
+        <v>85900</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -3462,16 +3462,16 @@
         <v>182</v>
       </c>
       <c r="B183">
-        <v>38182</v>
+        <v>38201</v>
       </c>
       <c r="C183">
-        <v>51510</v>
+        <v>51531</v>
       </c>
       <c r="D183">
-        <v>71155</v>
+        <v>71177</v>
       </c>
       <c r="E183">
-        <v>83397</v>
+        <v>83409</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -3479,16 +3479,16 @@
         <v>183</v>
       </c>
       <c r="B184">
-        <v>39282</v>
+        <v>39424</v>
       </c>
       <c r="C184">
-        <v>52589</v>
+        <v>52764</v>
       </c>
       <c r="D184">
-        <v>71444</v>
+        <v>71553</v>
       </c>
       <c r="E184">
-        <v>82997</v>
+        <v>83040</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -3496,16 +3496,16 @@
         <v>184</v>
       </c>
       <c r="B185">
-        <v>39282</v>
+        <v>39424</v>
       </c>
       <c r="C185">
-        <v>52589</v>
+        <v>52764</v>
       </c>
       <c r="D185">
-        <v>71444</v>
+        <v>71553</v>
       </c>
       <c r="E185">
-        <v>82997</v>
+        <v>83040</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -3513,13 +3513,13 @@
         <v>185</v>
       </c>
       <c r="B186">
-        <v>42295</v>
+        <v>42310</v>
       </c>
       <c r="C186">
-        <v>55946</v>
+        <v>55969</v>
       </c>
       <c r="D186">
-        <v>74074</v>
+        <v>74090</v>
       </c>
       <c r="E186">
         <v>85968</v>
@@ -3530,16 +3530,16 @@
         <v>186</v>
       </c>
       <c r="B187">
-        <v>37269</v>
+        <v>37359</v>
       </c>
       <c r="C187">
-        <v>49788</v>
+        <v>49906</v>
       </c>
       <c r="D187">
-        <v>68575</v>
+        <v>68676</v>
       </c>
       <c r="E187">
-        <v>80649</v>
+        <v>80694</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -3547,13 +3547,13 @@
         <v>187</v>
       </c>
       <c r="B188">
-        <v>40788</v>
+        <v>40824</v>
       </c>
       <c r="C188">
-        <v>54313</v>
+        <v>54346</v>
       </c>
       <c r="D188">
-        <v>72810</v>
+        <v>72828</v>
       </c>
       <c r="E188">
         <v>85124</v>
@@ -3564,16 +3564,16 @@
         <v>188</v>
       </c>
       <c r="B189">
-        <v>41821</v>
+        <v>41854</v>
       </c>
       <c r="C189">
-        <v>55667</v>
+        <v>55697</v>
       </c>
       <c r="D189">
-        <v>74723</v>
+        <v>74743</v>
       </c>
       <c r="E189">
-        <v>85921</v>
+        <v>85930</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -3581,16 +3581,16 @@
         <v>189</v>
       </c>
       <c r="B190">
-        <v>41821</v>
+        <v>41854</v>
       </c>
       <c r="C190">
-        <v>55667</v>
+        <v>55697</v>
       </c>
       <c r="D190">
-        <v>74723</v>
+        <v>74743</v>
       </c>
       <c r="E190">
-        <v>85921</v>
+        <v>85930</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -3598,16 +3598,16 @@
         <v>190</v>
       </c>
       <c r="B191">
-        <v>40033</v>
+        <v>40231</v>
       </c>
       <c r="C191">
-        <v>53222</v>
+        <v>53410</v>
       </c>
       <c r="D191">
-        <v>71799</v>
+        <v>71905</v>
       </c>
       <c r="E191">
-        <v>83223</v>
+        <v>83266</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -3615,16 +3615,16 @@
         <v>191</v>
       </c>
       <c r="B192">
-        <v>37269</v>
+        <v>37359</v>
       </c>
       <c r="C192">
-        <v>49788</v>
+        <v>49906</v>
       </c>
       <c r="D192">
-        <v>68575</v>
+        <v>68676</v>
       </c>
       <c r="E192">
-        <v>80649</v>
+        <v>80694</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -3632,16 +3632,16 @@
         <v>192</v>
       </c>
       <c r="B193">
-        <v>40856</v>
+        <v>41015</v>
       </c>
       <c r="C193">
-        <v>50366</v>
+        <v>50589</v>
       </c>
       <c r="D193">
-        <v>65623</v>
+        <v>66003</v>
       </c>
       <c r="E193">
-        <v>77557</v>
+        <v>77774</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -3649,16 +3649,16 @@
         <v>193</v>
       </c>
       <c r="B194">
-        <v>40505</v>
+        <v>40685</v>
       </c>
       <c r="C194">
-        <v>49436</v>
+        <v>49745</v>
       </c>
       <c r="D194">
-        <v>63627</v>
+        <v>64365</v>
       </c>
       <c r="E194">
-        <v>73941</v>
+        <v>75064</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -3666,16 +3666,16 @@
         <v>194</v>
       </c>
       <c r="B195">
-        <v>42753</v>
+        <v>42995</v>
       </c>
       <c r="C195">
-        <v>52314</v>
+        <v>52654</v>
       </c>
       <c r="D195">
-        <v>67211</v>
+        <v>67752</v>
       </c>
       <c r="E195">
-        <v>78581</v>
+        <v>78979</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -3683,16 +3683,16 @@
         <v>195</v>
       </c>
       <c r="B196">
-        <v>36494</v>
+        <v>36882</v>
       </c>
       <c r="C196">
-        <v>46638</v>
+        <v>47150</v>
       </c>
       <c r="D196">
-        <v>63023</v>
+        <v>63717</v>
       </c>
       <c r="E196">
-        <v>76149</v>
+        <v>76461</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -3700,16 +3700,16 @@
         <v>196</v>
       </c>
       <c r="B197">
-        <v>36835</v>
+        <v>37086</v>
       </c>
       <c r="C197">
-        <v>46721</v>
+        <v>47119</v>
       </c>
       <c r="D197">
-        <v>63034</v>
+        <v>63615</v>
       </c>
       <c r="E197">
-        <v>76059</v>
+        <v>76366</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -3717,16 +3717,16 @@
         <v>197</v>
       </c>
       <c r="B198">
-        <v>36586</v>
+        <v>36855</v>
       </c>
       <c r="C198">
-        <v>46040</v>
+        <v>46516</v>
       </c>
       <c r="D198">
-        <v>61599</v>
+        <v>62461</v>
       </c>
       <c r="E198">
-        <v>73705</v>
+        <v>74670</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -3734,16 +3734,16 @@
         <v>198</v>
       </c>
       <c r="B199">
-        <v>37498</v>
+        <v>37714</v>
       </c>
       <c r="C199">
-        <v>49618</v>
+        <v>49894</v>
       </c>
       <c r="D199">
-        <v>67089</v>
+        <v>67395</v>
       </c>
       <c r="E199">
-        <v>79204</v>
+        <v>79586</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -3751,16 +3751,16 @@
         <v>199</v>
       </c>
       <c r="B200">
-        <v>37851</v>
+        <v>38055</v>
       </c>
       <c r="C200">
-        <v>50298</v>
+        <v>50532</v>
       </c>
       <c r="D200">
-        <v>68368</v>
+        <v>68553</v>
       </c>
       <c r="E200">
-        <v>80658</v>
+        <v>80783</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -3768,16 +3768,16 @@
         <v>200</v>
       </c>
       <c r="B201">
-        <v>41347</v>
+        <v>41415</v>
       </c>
       <c r="C201">
-        <v>54278</v>
+        <v>54366</v>
       </c>
       <c r="D201">
-        <v>71600</v>
+        <v>71851</v>
       </c>
       <c r="E201">
-        <v>82215</v>
+        <v>82440</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -3785,16 +3785,16 @@
         <v>201</v>
       </c>
       <c r="B202">
-        <v>43066</v>
+        <v>43110</v>
       </c>
       <c r="C202">
-        <v>56793</v>
+        <v>56839</v>
       </c>
       <c r="D202">
-        <v>71460</v>
+        <v>71513</v>
       </c>
       <c r="E202">
-        <v>82814</v>
+        <v>82821</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -3802,16 +3802,16 @@
         <v>202</v>
       </c>
       <c r="B203">
-        <v>37886</v>
+        <v>38167</v>
       </c>
       <c r="C203">
-        <v>50457</v>
+        <v>50749</v>
       </c>
       <c r="D203">
-        <v>68399</v>
+        <v>68616</v>
       </c>
       <c r="E203">
-        <v>80653</v>
+        <v>80779</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -3819,16 +3819,16 @@
         <v>203</v>
       </c>
       <c r="B204">
-        <v>35295</v>
+        <v>35597</v>
       </c>
       <c r="C204">
-        <v>48522</v>
+        <v>48848</v>
       </c>
       <c r="D204">
-        <v>67383</v>
+        <v>67633</v>
       </c>
       <c r="E204">
-        <v>80038</v>
+        <v>80181</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -3836,16 +3836,16 @@
         <v>204</v>
       </c>
       <c r="B205">
-        <v>40006</v>
+        <v>40175</v>
       </c>
       <c r="C205">
-        <v>54075</v>
+        <v>54227</v>
       </c>
       <c r="D205">
-        <v>73112</v>
+        <v>73210</v>
       </c>
       <c r="E205">
-        <v>84390</v>
+        <v>84432</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -3853,16 +3853,16 @@
         <v>205</v>
       </c>
       <c r="B206">
-        <v>25329</v>
+        <v>25379</v>
       </c>
       <c r="C206">
-        <v>32305</v>
+        <v>32383</v>
       </c>
       <c r="D206">
-        <v>48837</v>
+        <v>49159</v>
       </c>
       <c r="E206">
-        <v>64099</v>
+        <v>64510</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -3870,16 +3870,16 @@
         <v>206</v>
       </c>
       <c r="B207">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="C207">
-        <v>27988</v>
+        <v>28096</v>
       </c>
       <c r="D207">
-        <v>43938</v>
+        <v>44249</v>
       </c>
       <c r="E207">
-        <v>59497</v>
+        <v>59912</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -3887,16 +3887,16 @@
         <v>207</v>
       </c>
       <c r="B208">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="C208">
-        <v>27988</v>
+        <v>28096</v>
       </c>
       <c r="D208">
-        <v>43938</v>
+        <v>44249</v>
       </c>
       <c r="E208">
-        <v>59497</v>
+        <v>59912</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -3904,16 +3904,16 @@
         <v>208</v>
       </c>
       <c r="B209">
-        <v>25225</v>
+        <v>25279</v>
       </c>
       <c r="C209">
-        <v>31685</v>
+        <v>31784</v>
       </c>
       <c r="D209">
-        <v>46465</v>
+        <v>46994</v>
       </c>
       <c r="E209">
-        <v>59630</v>
+        <v>61209</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -3921,16 +3921,16 @@
         <v>209</v>
       </c>
       <c r="B210">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="C210">
-        <v>27988</v>
+        <v>28096</v>
       </c>
       <c r="D210">
-        <v>43938</v>
+        <v>44249</v>
       </c>
       <c r="E210">
-        <v>59497</v>
+        <v>59912</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -3938,16 +3938,16 @@
         <v>210</v>
       </c>
       <c r="B211">
-        <v>21906</v>
+        <v>21966</v>
       </c>
       <c r="C211">
-        <v>30819</v>
+        <v>30882</v>
       </c>
       <c r="D211">
-        <v>51166</v>
+        <v>51265</v>
       </c>
       <c r="E211">
-        <v>66925</v>
+        <v>67098</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -3955,16 +3955,16 @@
         <v>211</v>
       </c>
       <c r="B212">
-        <v>24475</v>
+        <v>24515</v>
       </c>
       <c r="C212">
-        <v>35281</v>
+        <v>35326</v>
       </c>
       <c r="D212">
-        <v>56111</v>
+        <v>56275</v>
       </c>
       <c r="E212">
-        <v>70990</v>
+        <v>71215</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -3972,16 +3972,16 @@
         <v>212</v>
       </c>
       <c r="B213">
-        <v>21905</v>
+        <v>21979</v>
       </c>
       <c r="C213">
-        <v>27988</v>
+        <v>28096</v>
       </c>
       <c r="D213">
-        <v>43938</v>
+        <v>44249</v>
       </c>
       <c r="E213">
-        <v>59497</v>
+        <v>59912</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -3989,16 +3989,16 @@
         <v>213</v>
       </c>
       <c r="B214">
-        <v>18997</v>
+        <v>19037</v>
       </c>
       <c r="C214">
-        <v>26474</v>
+        <v>26536</v>
       </c>
       <c r="D214">
-        <v>45893</v>
+        <v>45972</v>
       </c>
       <c r="E214">
-        <v>61566</v>
+        <v>61727</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -4006,16 +4006,16 @@
         <v>214</v>
       </c>
       <c r="B215">
-        <v>18997</v>
+        <v>19037</v>
       </c>
       <c r="C215">
-        <v>26474</v>
+        <v>26536</v>
       </c>
       <c r="D215">
-        <v>45893</v>
+        <v>45972</v>
       </c>
       <c r="E215">
-        <v>61566</v>
+        <v>61727</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -4023,16 +4023,16 @@
         <v>215</v>
       </c>
       <c r="B216">
-        <v>16902</v>
+        <v>17016</v>
       </c>
       <c r="C216">
-        <v>24473</v>
+        <v>24590</v>
       </c>
       <c r="D216">
-        <v>44055</v>
+        <v>44174</v>
       </c>
       <c r="E216">
-        <v>60076</v>
+        <v>60251</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -4040,16 +4040,16 @@
         <v>216</v>
       </c>
       <c r="B217">
-        <v>19218</v>
+        <v>19261</v>
       </c>
       <c r="C217">
-        <v>27167</v>
+        <v>27216</v>
       </c>
       <c r="D217">
-        <v>47008</v>
+        <v>47089</v>
       </c>
       <c r="E217">
-        <v>62789</v>
+        <v>62974</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -4057,16 +4057,16 @@
         <v>217</v>
       </c>
       <c r="B218">
-        <v>21791</v>
+        <v>21814</v>
       </c>
       <c r="C218">
-        <v>32316</v>
+        <v>32339</v>
       </c>
       <c r="D218">
-        <v>54870</v>
+        <v>54908</v>
       </c>
       <c r="E218">
-        <v>70153</v>
+        <v>70220</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -4074,16 +4074,16 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>22798</v>
+        <v>22850</v>
       </c>
       <c r="C219">
-        <v>33505</v>
+        <v>33552</v>
       </c>
       <c r="D219">
-        <v>54749</v>
+        <v>54905</v>
       </c>
       <c r="E219">
-        <v>69972</v>
+        <v>70185</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -4091,16 +4091,16 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>24260</v>
+        <v>24327</v>
       </c>
       <c r="C220">
-        <v>36052</v>
+        <v>36120</v>
       </c>
       <c r="D220">
-        <v>57465</v>
+        <v>57742</v>
       </c>
       <c r="E220">
-        <v>72306</v>
+        <v>72558</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -4108,16 +4108,16 @@
         <v>220</v>
       </c>
       <c r="B221">
-        <v>27655</v>
+        <v>27685</v>
       </c>
       <c r="C221">
-        <v>41345</v>
+        <v>41387</v>
       </c>
       <c r="D221">
-        <v>63643</v>
+        <v>63719</v>
       </c>
       <c r="E221">
-        <v>77192</v>
+        <v>77257</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -4125,16 +4125,16 @@
         <v>221</v>
       </c>
       <c r="B222">
-        <v>22798</v>
+        <v>22850</v>
       </c>
       <c r="C222">
-        <v>33505</v>
+        <v>33552</v>
       </c>
       <c r="D222">
-        <v>54749</v>
+        <v>54905</v>
       </c>
       <c r="E222">
-        <v>69972</v>
+        <v>70185</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -4142,16 +4142,16 @@
         <v>222</v>
       </c>
       <c r="B223">
-        <v>34601</v>
+        <v>34606</v>
       </c>
       <c r="C223">
-        <v>51372</v>
+        <v>51376</v>
       </c>
       <c r="D223">
-        <v>73084</v>
+        <v>73098</v>
       </c>
       <c r="E223">
-        <v>84608</v>
+        <v>84624</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -4159,16 +4159,16 @@
         <v>223</v>
       </c>
       <c r="B224">
-        <v>21354</v>
+        <v>21531</v>
       </c>
       <c r="C224">
-        <v>33169</v>
+        <v>33243</v>
       </c>
       <c r="D224">
-        <v>57472</v>
+        <v>57494</v>
       </c>
       <c r="E224">
-        <v>74587</v>
+        <v>74592</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -4176,16 +4176,16 @@
         <v>224</v>
       </c>
       <c r="B225">
-        <v>15551</v>
+        <v>15935</v>
       </c>
       <c r="C225">
-        <v>22847</v>
+        <v>23086</v>
       </c>
       <c r="D225">
-        <v>41869</v>
+        <v>42021</v>
       </c>
       <c r="E225">
-        <v>58238</v>
+        <v>58373</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -4193,16 +4193,16 @@
         <v>225</v>
       </c>
       <c r="B226">
-        <v>17834</v>
+        <v>18095</v>
       </c>
       <c r="C226">
-        <v>26911</v>
+        <v>27052</v>
       </c>
       <c r="D226">
-        <v>49290</v>
+        <v>49358</v>
       </c>
       <c r="E226">
-        <v>66056</v>
+        <v>66108</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -4210,16 +4210,16 @@
         <v>226</v>
       </c>
       <c r="B227">
-        <v>17065</v>
+        <v>17136</v>
       </c>
       <c r="C227">
-        <v>23150</v>
+        <v>23303</v>
       </c>
       <c r="D227">
-        <v>38594</v>
+        <v>38897</v>
       </c>
       <c r="E227">
-        <v>52093</v>
+        <v>52890</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -4227,16 +4227,16 @@
         <v>227</v>
       </c>
       <c r="B228">
-        <v>18767</v>
+        <v>18804</v>
       </c>
       <c r="C228">
-        <v>29758</v>
+        <v>29779</v>
       </c>
       <c r="D228">
-        <v>55476</v>
+        <v>55486</v>
       </c>
       <c r="E228">
-        <v>74286</v>
+        <v>74287</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -4244,16 +4244,16 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>24260</v>
+        <v>24327</v>
       </c>
       <c r="C229">
-        <v>36052</v>
+        <v>36120</v>
       </c>
       <c r="D229">
-        <v>57465</v>
+        <v>57742</v>
       </c>
       <c r="E229">
-        <v>72306</v>
+        <v>72558</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -4261,16 +4261,16 @@
         <v>229</v>
       </c>
       <c r="B230">
-        <v>23901</v>
+        <v>23963</v>
       </c>
       <c r="C230">
-        <v>34959</v>
+        <v>35053</v>
       </c>
       <c r="D230">
-        <v>55941</v>
+        <v>56110</v>
       </c>
       <c r="E230">
-        <v>70853</v>
+        <v>71051</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -4278,16 +4278,16 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>28311</v>
+        <v>28339</v>
       </c>
       <c r="C231">
-        <v>41623</v>
+        <v>41648</v>
       </c>
       <c r="D231">
-        <v>63698</v>
+        <v>63785</v>
       </c>
       <c r="E231">
-        <v>77225</v>
+        <v>77300</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -4295,16 +4295,16 @@
         <v>231</v>
       </c>
       <c r="B232">
-        <v>24841</v>
+        <v>24848</v>
       </c>
       <c r="C232">
-        <v>36831</v>
+        <v>36841</v>
       </c>
       <c r="D232">
-        <v>59325</v>
+        <v>59370</v>
       </c>
       <c r="E232">
-        <v>73811</v>
+        <v>73882</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -4312,16 +4312,16 @@
         <v>232</v>
       </c>
       <c r="B233">
-        <v>30584</v>
+        <v>30586</v>
       </c>
       <c r="C233">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="D233">
-        <v>69077</v>
+        <v>69091</v>
       </c>
       <c r="E233">
-        <v>81774</v>
+        <v>81797</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -4329,13 +4329,13 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>33827</v>
+        <v>33835</v>
       </c>
       <c r="C234">
-        <v>49100</v>
+        <v>49103</v>
       </c>
       <c r="D234">
-        <v>69830</v>
+        <v>69834</v>
       </c>
       <c r="E234">
         <v>82731</v>
@@ -4346,13 +4346,13 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>33827</v>
+        <v>33835</v>
       </c>
       <c r="C235">
-        <v>49100</v>
+        <v>49103</v>
       </c>
       <c r="D235">
-        <v>69830</v>
+        <v>69834</v>
       </c>
       <c r="E235">
         <v>82731</v>
@@ -4363,16 +4363,16 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>34260</v>
+        <v>34266</v>
       </c>
       <c r="C236">
-        <v>50439</v>
+        <v>50442</v>
       </c>
       <c r="D236">
-        <v>71848</v>
+        <v>71853</v>
       </c>
       <c r="E236">
-        <v>83561</v>
+        <v>83575</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -4380,16 +4380,16 @@
         <v>236</v>
       </c>
       <c r="B237">
-        <v>19567</v>
+        <v>19599</v>
       </c>
       <c r="C237">
-        <v>28190</v>
+        <v>28241</v>
       </c>
       <c r="D237">
-        <v>49587</v>
+        <v>49628</v>
       </c>
       <c r="E237">
-        <v>65738</v>
+        <v>65777</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -4397,16 +4397,16 @@
         <v>237</v>
       </c>
       <c r="B238">
-        <v>17561</v>
+        <v>17621</v>
       </c>
       <c r="C238">
-        <v>24424</v>
+        <v>24524</v>
       </c>
       <c r="D238">
-        <v>42614</v>
+        <v>42718</v>
       </c>
       <c r="E238">
-        <v>58231</v>
+        <v>58343</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -4414,16 +4414,16 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>23094</v>
+        <v>23101</v>
       </c>
       <c r="C239">
-        <v>35117</v>
+        <v>35123</v>
       </c>
       <c r="D239">
-        <v>59318</v>
+        <v>59322</v>
       </c>
       <c r="E239">
-        <v>74927</v>
+        <v>74939</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -4431,16 +4431,16 @@
         <v>239</v>
       </c>
       <c r="B240">
-        <v>20493</v>
+        <v>20506</v>
       </c>
       <c r="C240">
-        <v>31655</v>
+        <v>31662</v>
       </c>
       <c r="D240">
-        <v>54901</v>
+        <v>54908</v>
       </c>
       <c r="E240">
-        <v>71550</v>
+        <v>71551</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -4448,16 +4448,16 @@
         <v>240</v>
       </c>
       <c r="B241">
-        <v>21006</v>
+        <v>21020</v>
       </c>
       <c r="C241">
-        <v>33333</v>
+        <v>33341</v>
       </c>
       <c r="D241">
-        <v>58032</v>
+        <v>58040</v>
       </c>
       <c r="E241">
-        <v>73565</v>
+        <v>73584</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -4465,16 +4465,16 @@
         <v>241</v>
       </c>
       <c r="B242">
-        <v>27655</v>
+        <v>27685</v>
       </c>
       <c r="C242">
-        <v>41345</v>
+        <v>41387</v>
       </c>
       <c r="D242">
-        <v>63643</v>
+        <v>63719</v>
       </c>
       <c r="E242">
-        <v>77192</v>
+        <v>77257</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -4482,16 +4482,16 @@
         <v>242</v>
       </c>
       <c r="B243">
-        <v>29303</v>
+        <v>29389</v>
       </c>
       <c r="C243">
-        <v>44198</v>
+        <v>44277</v>
       </c>
       <c r="D243">
-        <v>65963</v>
+        <v>66069</v>
       </c>
       <c r="E243">
-        <v>78778</v>
+        <v>78846</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -4499,16 +4499,16 @@
         <v>243</v>
       </c>
       <c r="B244">
-        <v>27655</v>
+        <v>27685</v>
       </c>
       <c r="C244">
-        <v>41345</v>
+        <v>41387</v>
       </c>
       <c r="D244">
-        <v>63643</v>
+        <v>63719</v>
       </c>
       <c r="E244">
-        <v>77192</v>
+        <v>77257</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -4516,13 +4516,13 @@
         <v>244</v>
       </c>
       <c r="B245">
-        <v>36144</v>
+        <v>36163</v>
       </c>
       <c r="C245">
-        <v>52748</v>
+        <v>52765</v>
       </c>
       <c r="D245">
-        <v>72952</v>
+        <v>72971</v>
       </c>
       <c r="E245">
         <v>84941</v>
@@ -4533,13 +4533,13 @@
         <v>245</v>
       </c>
       <c r="B246">
-        <v>35804</v>
+        <v>35823</v>
       </c>
       <c r="C246">
-        <v>52778</v>
+        <v>52793</v>
       </c>
       <c r="D246">
-        <v>73362</v>
+        <v>73383</v>
       </c>
       <c r="E246">
         <v>85384</v>
@@ -4550,13 +4550,13 @@
         <v>246</v>
       </c>
       <c r="B247">
-        <v>35804</v>
+        <v>35823</v>
       </c>
       <c r="C247">
-        <v>52778</v>
+        <v>52793</v>
       </c>
       <c r="D247">
-        <v>73362</v>
+        <v>73383</v>
       </c>
       <c r="E247">
         <v>85384</v>
@@ -4567,13 +4567,13 @@
         <v>247</v>
       </c>
       <c r="B248">
-        <v>29542</v>
+        <v>29557</v>
       </c>
       <c r="C248">
-        <v>43837</v>
+        <v>43844</v>
       </c>
       <c r="D248">
-        <v>66425</v>
+        <v>66435</v>
       </c>
       <c r="E248">
         <v>80940</v>
@@ -4584,16 +4584,16 @@
         <v>248</v>
       </c>
       <c r="B249">
-        <v>19486</v>
+        <v>19518</v>
       </c>
       <c r="C249">
-        <v>31042</v>
+        <v>31060</v>
       </c>
       <c r="D249">
-        <v>57550</v>
+        <v>57561</v>
       </c>
       <c r="E249">
-        <v>75311</v>
+        <v>75329</v>
       </c>
     </row>
     <row r="250" spans="1:5">
@@ -4601,16 +4601,16 @@
         <v>249</v>
       </c>
       <c r="B250">
-        <v>34471</v>
+        <v>34513</v>
       </c>
       <c r="C250">
-        <v>49824</v>
+        <v>49912</v>
       </c>
       <c r="D250">
-        <v>69611</v>
+        <v>69711</v>
       </c>
       <c r="E250">
-        <v>81341</v>
+        <v>81390</v>
       </c>
     </row>
     <row r="251" spans="1:5">
@@ -4618,16 +4618,16 @@
         <v>250</v>
       </c>
       <c r="B251">
-        <v>39665</v>
+        <v>39745</v>
       </c>
       <c r="C251">
-        <v>54345</v>
+        <v>54445</v>
       </c>
       <c r="D251">
-        <v>73006</v>
+        <v>73123</v>
       </c>
       <c r="E251">
-        <v>83897</v>
+        <v>83946</v>
       </c>
     </row>
     <row r="252" spans="1:5">
@@ -4635,16 +4635,16 @@
         <v>251</v>
       </c>
       <c r="B252">
-        <v>35169</v>
+        <v>35184</v>
       </c>
       <c r="C252">
-        <v>49270</v>
+        <v>49288</v>
       </c>
       <c r="D252">
-        <v>68849</v>
+        <v>68893</v>
       </c>
       <c r="E252">
-        <v>80770</v>
+        <v>80814</v>
       </c>
     </row>
     <row r="253" spans="1:5">
@@ -4652,16 +4652,16 @@
         <v>252</v>
       </c>
       <c r="B253">
-        <v>41169</v>
+        <v>41177</v>
       </c>
       <c r="C253">
-        <v>57687</v>
+        <v>57706</v>
       </c>
       <c r="D253">
-        <v>77122</v>
+        <v>77138</v>
       </c>
       <c r="E253">
-        <v>87406</v>
+        <v>87416</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -4669,16 +4669,16 @@
         <v>253</v>
       </c>
       <c r="B254">
-        <v>45902</v>
+        <v>45920</v>
       </c>
       <c r="C254">
-        <v>61644</v>
+        <v>61668</v>
       </c>
       <c r="D254">
-        <v>79677</v>
+        <v>79691</v>
       </c>
       <c r="E254">
-        <v>89280</v>
+        <v>89287</v>
       </c>
     </row>
     <row r="255" spans="1:5">
@@ -4686,16 +4686,16 @@
         <v>254</v>
       </c>
       <c r="B255">
-        <v>41169</v>
+        <v>41177</v>
       </c>
       <c r="C255">
-        <v>57687</v>
+        <v>57706</v>
       </c>
       <c r="D255">
-        <v>77122</v>
+        <v>77138</v>
       </c>
       <c r="E255">
-        <v>87406</v>
+        <v>87416</v>
       </c>
     </row>
     <row r="256" spans="1:5">
@@ -4703,16 +4703,16 @@
         <v>255</v>
       </c>
       <c r="B256">
-        <v>39553</v>
+        <v>39555</v>
       </c>
       <c r="C256">
-        <v>55590</v>
+        <v>55593</v>
       </c>
       <c r="D256">
-        <v>75143</v>
+        <v>75148</v>
       </c>
       <c r="E256">
-        <v>85805</v>
+        <v>85815</v>
       </c>
     </row>
     <row r="257" spans="1:5">
@@ -4720,16 +4720,16 @@
         <v>256</v>
       </c>
       <c r="B257">
-        <v>30750</v>
+        <v>30752</v>
       </c>
       <c r="C257">
-        <v>48093</v>
+        <v>48098</v>
       </c>
       <c r="D257">
-        <v>70364</v>
+        <v>70380</v>
       </c>
       <c r="E257">
-        <v>82394</v>
+        <v>82413</v>
       </c>
     </row>
     <row r="258" spans="1:5">
@@ -4737,16 +4737,16 @@
         <v>257</v>
       </c>
       <c r="B258">
-        <v>29523</v>
+        <v>29524</v>
       </c>
       <c r="C258">
-        <v>46399</v>
+        <v>46401</v>
       </c>
       <c r="D258">
-        <v>68711</v>
+        <v>68718</v>
       </c>
       <c r="E258">
-        <v>81110</v>
+        <v>81128</v>
       </c>
     </row>
     <row r="259" spans="1:5">
@@ -4754,16 +4754,16 @@
         <v>258</v>
       </c>
       <c r="B259">
-        <v>29523</v>
+        <v>29524</v>
       </c>
       <c r="C259">
-        <v>46399</v>
+        <v>46401</v>
       </c>
       <c r="D259">
-        <v>68711</v>
+        <v>68718</v>
       </c>
       <c r="E259">
-        <v>81110</v>
+        <v>81128</v>
       </c>
     </row>
     <row r="260" spans="1:5">
@@ -4771,16 +4771,16 @@
         <v>259</v>
       </c>
       <c r="B260">
-        <v>12174</v>
+        <v>12200</v>
       </c>
       <c r="C260">
-        <v>23844</v>
+        <v>23897</v>
       </c>
       <c r="D260">
-        <v>48446</v>
+        <v>48539</v>
       </c>
       <c r="E260">
-        <v>65534</v>
+        <v>65611</v>
       </c>
     </row>
     <row r="261" spans="1:5">
@@ -4788,16 +4788,16 @@
         <v>260</v>
       </c>
       <c r="B261">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="C261">
-        <v>22090</v>
+        <v>22091</v>
       </c>
       <c r="D261">
-        <v>48863</v>
+        <v>48869</v>
       </c>
       <c r="E261">
-        <v>66955</v>
+        <v>66971</v>
       </c>
     </row>
     <row r="262" spans="1:5">
@@ -4805,16 +4805,16 @@
         <v>261</v>
       </c>
       <c r="B262">
-        <v>12361</v>
+        <v>12375</v>
       </c>
       <c r="C262">
-        <v>23776</v>
+        <v>23823</v>
       </c>
       <c r="D262">
-        <v>47860</v>
+        <v>47947</v>
       </c>
       <c r="E262">
-        <v>64779</v>
+        <v>64854</v>
       </c>
     </row>
     <row r="263" spans="1:5">
@@ -4822,13 +4822,13 @@
         <v>262</v>
       </c>
       <c r="B263">
-        <v>16717</v>
+        <v>16719</v>
       </c>
       <c r="C263">
-        <v>30801</v>
+        <v>30805</v>
       </c>
       <c r="D263">
-        <v>55463</v>
+        <v>55479</v>
       </c>
       <c r="E263">
         <v>72624</v>
@@ -4839,16 +4839,16 @@
         <v>263</v>
       </c>
       <c r="B264">
-        <v>14842</v>
+        <v>14845</v>
       </c>
       <c r="C264">
-        <v>28052</v>
+        <v>28053</v>
       </c>
       <c r="D264">
-        <v>53393</v>
+        <v>53399</v>
       </c>
       <c r="E264">
-        <v>70198</v>
+        <v>70218</v>
       </c>
     </row>
     <row r="265" spans="1:5">
@@ -4856,16 +4856,16 @@
         <v>264</v>
       </c>
       <c r="B265">
-        <v>14842</v>
+        <v>14845</v>
       </c>
       <c r="C265">
-        <v>28052</v>
+        <v>28053</v>
       </c>
       <c r="D265">
-        <v>53393</v>
+        <v>53399</v>
       </c>
       <c r="E265">
-        <v>70198</v>
+        <v>70218</v>
       </c>
     </row>
     <row r="266" spans="1:5">
@@ -4873,16 +4873,16 @@
         <v>265</v>
       </c>
       <c r="B266">
-        <v>22403</v>
+        <v>22406</v>
       </c>
       <c r="C266">
-        <v>38239</v>
+        <v>38250</v>
       </c>
       <c r="D266">
-        <v>62775</v>
+        <v>62806</v>
       </c>
       <c r="E266">
-        <v>78021</v>
+        <v>78046</v>
       </c>
     </row>
     <row r="267" spans="1:5">
@@ -4890,16 +4890,16 @@
         <v>266</v>
       </c>
       <c r="B267">
-        <v>14842</v>
+        <v>14845</v>
       </c>
       <c r="C267">
-        <v>28052</v>
+        <v>28053</v>
       </c>
       <c r="D267">
-        <v>53393</v>
+        <v>53399</v>
       </c>
       <c r="E267">
-        <v>70198</v>
+        <v>70218</v>
       </c>
     </row>
     <row r="268" spans="1:5">
@@ -4907,16 +4907,16 @@
         <v>267</v>
       </c>
       <c r="B268">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="C268">
-        <v>22090</v>
+        <v>22091</v>
       </c>
       <c r="D268">
-        <v>48863</v>
+        <v>48869</v>
       </c>
       <c r="E268">
-        <v>66955</v>
+        <v>66971</v>
       </c>
     </row>
     <row r="269" spans="1:5">
@@ -4924,16 +4924,16 @@
         <v>268</v>
       </c>
       <c r="B269">
-        <v>9928</v>
+        <v>9929</v>
       </c>
       <c r="C269">
-        <v>22090</v>
+        <v>22091</v>
       </c>
       <c r="D269">
-        <v>48863</v>
+        <v>48869</v>
       </c>
       <c r="E269">
-        <v>66955</v>
+        <v>66971</v>
       </c>
     </row>
     <row r="270" spans="1:5">
@@ -4941,16 +4941,16 @@
         <v>269</v>
       </c>
       <c r="B270">
-        <v>13328</v>
+        <v>13334</v>
       </c>
       <c r="C270">
-        <v>27868</v>
+        <v>27872</v>
       </c>
       <c r="D270">
-        <v>54610</v>
+        <v>54619</v>
       </c>
       <c r="E270">
-        <v>71195</v>
+        <v>71215</v>
       </c>
     </row>
     <row r="271" spans="1:5">
@@ -4958,16 +4958,16 @@
         <v>270</v>
       </c>
       <c r="B271">
-        <v>8342</v>
+        <v>8350</v>
       </c>
       <c r="C271">
-        <v>19333</v>
+        <v>19338</v>
       </c>
       <c r="D271">
-        <v>45469</v>
+        <v>45473</v>
       </c>
       <c r="E271">
-        <v>63499</v>
+        <v>63510</v>
       </c>
     </row>
     <row r="272" spans="1:5">
@@ -4975,16 +4975,16 @@
         <v>271</v>
       </c>
       <c r="B272">
-        <v>8342</v>
+        <v>8350</v>
       </c>
       <c r="C272">
-        <v>19333</v>
+        <v>19338</v>
       </c>
       <c r="D272">
-        <v>45469</v>
+        <v>45473</v>
       </c>
       <c r="E272">
-        <v>63499</v>
+        <v>63510</v>
       </c>
     </row>
     <row r="273" spans="1:5">
@@ -4992,16 +4992,16 @@
         <v>272</v>
       </c>
       <c r="B273">
-        <v>15587</v>
+        <v>15588</v>
       </c>
       <c r="C273">
-        <v>31202</v>
+        <v>31206</v>
       </c>
       <c r="D273">
-        <v>57562</v>
+        <v>57576</v>
       </c>
       <c r="E273">
-        <v>73640</v>
+        <v>73663</v>
       </c>
     </row>
     <row r="274" spans="1:5">
@@ -5009,16 +5009,16 @@
         <v>273</v>
       </c>
       <c r="B274">
-        <v>15587</v>
+        <v>15588</v>
       </c>
       <c r="C274">
-        <v>31202</v>
+        <v>31206</v>
       </c>
       <c r="D274">
-        <v>57562</v>
+        <v>57576</v>
       </c>
       <c r="E274">
-        <v>73640</v>
+        <v>73663</v>
       </c>
     </row>
     <row r="275" spans="1:5">
@@ -5026,16 +5026,16 @@
         <v>274</v>
       </c>
       <c r="B275">
-        <v>8415</v>
+        <v>8427</v>
       </c>
       <c r="C275">
-        <v>14898</v>
+        <v>14911</v>
       </c>
       <c r="D275">
-        <v>35402</v>
+        <v>35432</v>
       </c>
       <c r="E275">
-        <v>53307</v>
+        <v>53329</v>
       </c>
     </row>
     <row r="276" spans="1:5">
@@ -5043,16 +5043,16 @@
         <v>275</v>
       </c>
       <c r="B276">
-        <v>6867</v>
+        <v>6870</v>
       </c>
       <c r="C276">
-        <v>13968</v>
+        <v>13969</v>
       </c>
       <c r="D276">
-        <v>36016</v>
+        <v>36019</v>
       </c>
       <c r="E276">
-        <v>55111</v>
+        <v>55116</v>
       </c>
     </row>
     <row r="277" spans="1:5">
@@ -5060,16 +5060,16 @@
         <v>276</v>
       </c>
       <c r="B277">
-        <v>14440</v>
+        <v>14442</v>
       </c>
       <c r="C277">
-        <v>24927</v>
+        <v>24933</v>
       </c>
       <c r="D277">
-        <v>51322</v>
+        <v>51329</v>
       </c>
       <c r="E277">
-        <v>70723</v>
+        <v>70728</v>
       </c>
     </row>
     <row r="278" spans="1:5">
@@ -5077,16 +5077,16 @@
         <v>277</v>
       </c>
       <c r="B278">
-        <v>20196</v>
+        <v>20222</v>
       </c>
       <c r="C278">
-        <v>34865</v>
+        <v>34881</v>
       </c>
       <c r="D278">
-        <v>62603</v>
+        <v>62608</v>
       </c>
       <c r="E278">
-        <v>79602</v>
+        <v>79608</v>
       </c>
     </row>
     <row r="279" spans="1:5">
@@ -5094,16 +5094,16 @@
         <v>278</v>
       </c>
       <c r="B279">
-        <v>20113</v>
+        <v>20144</v>
       </c>
       <c r="C279">
-        <v>32607</v>
+        <v>32620</v>
       </c>
       <c r="D279">
-        <v>59137</v>
+        <v>59141</v>
       </c>
       <c r="E279">
-        <v>76461</v>
+        <v>76469</v>
       </c>
     </row>
     <row r="280" spans="1:5">
@@ -5111,16 +5111,16 @@
         <v>279</v>
       </c>
       <c r="B280">
-        <v>20113</v>
+        <v>20144</v>
       </c>
       <c r="C280">
-        <v>32607</v>
+        <v>32620</v>
       </c>
       <c r="D280">
-        <v>59137</v>
+        <v>59141</v>
       </c>
       <c r="E280">
-        <v>76461</v>
+        <v>76469</v>
       </c>
     </row>
     <row r="281" spans="1:5">
@@ -5128,16 +5128,16 @@
         <v>280</v>
       </c>
       <c r="B281">
-        <v>7815</v>
+        <v>7819</v>
       </c>
       <c r="C281">
-        <v>15885</v>
+        <v>15887</v>
       </c>
       <c r="D281">
-        <v>39769</v>
+        <v>39773</v>
       </c>
       <c r="E281">
-        <v>59818</v>
+        <v>59825</v>
       </c>
     </row>
     <row r="282" spans="1:5">
@@ -5145,16 +5145,16 @@
         <v>281</v>
       </c>
       <c r="B282">
-        <v>6865</v>
+        <v>6883</v>
       </c>
       <c r="C282">
-        <v>13932</v>
+        <v>13938</v>
       </c>
       <c r="D282">
-        <v>36047</v>
+        <v>36051</v>
       </c>
       <c r="E282">
-        <v>55193</v>
+        <v>55199</v>
       </c>
     </row>
     <row r="283" spans="1:5">
@@ -5162,16 +5162,16 @@
         <v>282</v>
       </c>
       <c r="B283">
-        <v>6865</v>
+        <v>6883</v>
       </c>
       <c r="C283">
-        <v>13932</v>
+        <v>13938</v>
       </c>
       <c r="D283">
-        <v>36047</v>
+        <v>36051</v>
       </c>
       <c r="E283">
-        <v>55193</v>
+        <v>55199</v>
       </c>
     </row>
     <row r="284" spans="1:5">
@@ -5179,16 +5179,16 @@
         <v>283</v>
       </c>
       <c r="B284">
-        <v>6865</v>
+        <v>6883</v>
       </c>
       <c r="C284">
-        <v>13932</v>
+        <v>13938</v>
       </c>
       <c r="D284">
-        <v>36047</v>
+        <v>36051</v>
       </c>
       <c r="E284">
-        <v>55193</v>
+        <v>55199</v>
       </c>
     </row>
     <row r="285" spans="1:5">
@@ -5196,16 +5196,16 @@
         <v>284</v>
       </c>
       <c r="B285">
-        <v>6867</v>
+        <v>6870</v>
       </c>
       <c r="C285">
-        <v>13968</v>
+        <v>13969</v>
       </c>
       <c r="D285">
-        <v>36016</v>
+        <v>36019</v>
       </c>
       <c r="E285">
-        <v>55111</v>
+        <v>55116</v>
       </c>
     </row>
     <row r="286" spans="1:5">
@@ -5213,16 +5213,16 @@
         <v>285</v>
       </c>
       <c r="B286">
-        <v>20113</v>
+        <v>20144</v>
       </c>
       <c r="C286">
-        <v>32607</v>
+        <v>32620</v>
       </c>
       <c r="D286">
-        <v>59137</v>
+        <v>59141</v>
       </c>
       <c r="E286">
-        <v>76461</v>
+        <v>76469</v>
       </c>
     </row>
     <row r="287" spans="1:5">
@@ -5230,13 +5230,13 @@
         <v>286</v>
       </c>
       <c r="B287">
-        <v>32474</v>
+        <v>32482</v>
       </c>
       <c r="C287">
-        <v>47553</v>
+        <v>47565</v>
       </c>
       <c r="D287">
-        <v>68288</v>
+        <v>68308</v>
       </c>
       <c r="E287">
         <v>82371</v>
@@ -5247,13 +5247,13 @@
         <v>287</v>
       </c>
       <c r="B288">
-        <v>27711</v>
+        <v>27718</v>
       </c>
       <c r="C288">
-        <v>43512</v>
+        <v>43523</v>
       </c>
       <c r="D288">
-        <v>65560</v>
+        <v>65587</v>
       </c>
       <c r="E288">
         <v>80102</v>
@@ -5264,16 +5264,16 @@
         <v>288</v>
       </c>
       <c r="B289">
-        <v>36905</v>
+        <v>36952</v>
       </c>
       <c r="C289">
-        <v>51809</v>
+        <v>51856</v>
       </c>
       <c r="D289">
-        <v>72410</v>
+        <v>72443</v>
       </c>
       <c r="E289">
-        <v>84736</v>
+        <v>84750</v>
       </c>
     </row>
     <row r="290" spans="1:5">
@@ -5281,16 +5281,16 @@
         <v>289</v>
       </c>
       <c r="B290">
-        <v>33646</v>
+        <v>33653</v>
       </c>
       <c r="C290">
-        <v>48997</v>
+        <v>49008</v>
       </c>
       <c r="D290">
-        <v>70209</v>
+        <v>70230</v>
       </c>
       <c r="E290">
-        <v>83205</v>
+        <v>83217</v>
       </c>
     </row>
     <row r="291" spans="1:5">
@@ -5298,13 +5298,13 @@
         <v>290</v>
       </c>
       <c r="B291">
-        <v>25287</v>
+        <v>25294</v>
       </c>
       <c r="C291">
-        <v>41016</v>
+        <v>41027</v>
       </c>
       <c r="D291">
-        <v>63469</v>
+        <v>63494</v>
       </c>
       <c r="E291">
         <v>78309</v>
@@ -5315,13 +5315,13 @@
         <v>291</v>
       </c>
       <c r="B292">
-        <v>27447</v>
+        <v>27453</v>
       </c>
       <c r="C292">
-        <v>43992</v>
+        <v>44000</v>
       </c>
       <c r="D292">
-        <v>65806</v>
+        <v>65829</v>
       </c>
       <c r="E292">
         <v>79514</v>
@@ -5332,13 +5332,13 @@
         <v>292</v>
       </c>
       <c r="B293">
-        <v>27939</v>
+        <v>27949</v>
       </c>
       <c r="C293">
-        <v>44422</v>
+        <v>44432</v>
       </c>
       <c r="D293">
-        <v>66075</v>
+        <v>66093</v>
       </c>
       <c r="E293">
         <v>79893</v>
@@ -5349,16 +5349,16 @@
         <v>293</v>
       </c>
       <c r="B294">
-        <v>28951</v>
+        <v>28957</v>
       </c>
       <c r="C294">
-        <v>45791</v>
+        <v>45798</v>
       </c>
       <c r="D294">
-        <v>67886</v>
+        <v>67911</v>
       </c>
       <c r="E294">
-        <v>80428</v>
+        <v>80450</v>
       </c>
     </row>
     <row r="295" spans="1:5">
@@ -5366,16 +5366,16 @@
         <v>294</v>
       </c>
       <c r="B295">
-        <v>16731</v>
+        <v>16762</v>
       </c>
       <c r="C295">
-        <v>27804</v>
+        <v>27850</v>
       </c>
       <c r="D295">
-        <v>49302</v>
+        <v>49387</v>
       </c>
       <c r="E295">
-        <v>65368</v>
+        <v>65499</v>
       </c>
     </row>
     <row r="296" spans="1:5">
@@ -5383,16 +5383,16 @@
         <v>295</v>
       </c>
       <c r="B296">
-        <v>19925</v>
+        <v>19940</v>
       </c>
       <c r="C296">
-        <v>31287</v>
+        <v>31305</v>
       </c>
       <c r="D296">
-        <v>52510</v>
+        <v>52587</v>
       </c>
       <c r="E296">
-        <v>68285</v>
+        <v>68413</v>
       </c>
     </row>
     <row r="297" spans="1:5">
@@ -5400,16 +5400,16 @@
         <v>296</v>
       </c>
       <c r="B297">
-        <v>23232</v>
+        <v>23240</v>
       </c>
       <c r="C297">
-        <v>37321</v>
+        <v>37333</v>
       </c>
       <c r="D297">
-        <v>60837</v>
+        <v>60898</v>
       </c>
       <c r="E297">
-        <v>75881</v>
+        <v>75935</v>
       </c>
     </row>
     <row r="298" spans="1:5">
@@ -5417,16 +5417,16 @@
         <v>297</v>
       </c>
       <c r="B298">
-        <v>17641</v>
+        <v>17655</v>
       </c>
       <c r="C298">
-        <v>28651</v>
+        <v>28669</v>
       </c>
       <c r="D298">
-        <v>49925</v>
+        <v>49992</v>
       </c>
       <c r="E298">
-        <v>66046</v>
+        <v>66168</v>
       </c>
     </row>
     <row r="299" spans="1:5">
@@ -5434,16 +5434,16 @@
         <v>298</v>
       </c>
       <c r="B299">
-        <v>20125</v>
+        <v>20138</v>
       </c>
       <c r="C299">
-        <v>33552</v>
+        <v>33564</v>
       </c>
       <c r="D299">
-        <v>57273</v>
+        <v>57310</v>
       </c>
       <c r="E299">
-        <v>72903</v>
+        <v>72953</v>
       </c>
     </row>
     <row r="300" spans="1:5">
@@ -5451,16 +5451,16 @@
         <v>299</v>
       </c>
       <c r="B300">
-        <v>16731</v>
+        <v>16762</v>
       </c>
       <c r="C300">
-        <v>27804</v>
+        <v>27850</v>
       </c>
       <c r="D300">
-        <v>49302</v>
+        <v>49387</v>
       </c>
       <c r="E300">
-        <v>65368</v>
+        <v>65499</v>
       </c>
     </row>
     <row r="301" spans="1:5">
@@ -5468,16 +5468,16 @@
         <v>300</v>
       </c>
       <c r="B301">
-        <v>23494</v>
+        <v>23503</v>
       </c>
       <c r="C301">
-        <v>36872</v>
+        <v>36883</v>
       </c>
       <c r="D301">
-        <v>59773</v>
+        <v>59809</v>
       </c>
       <c r="E301">
-        <v>74847</v>
+        <v>74893</v>
       </c>
     </row>
     <row r="302" spans="1:5">
@@ -5485,13 +5485,13 @@
         <v>301</v>
       </c>
       <c r="B302">
-        <v>26316</v>
+        <v>26320</v>
       </c>
       <c r="C302">
-        <v>41460</v>
+        <v>41462</v>
       </c>
       <c r="D302">
-        <v>64747</v>
+        <v>64753</v>
       </c>
       <c r="E302">
         <v>80236</v>
@@ -5502,16 +5502,16 @@
         <v>302</v>
       </c>
       <c r="B303">
-        <v>27199</v>
+        <v>27202</v>
       </c>
       <c r="C303">
-        <v>42895</v>
+        <v>42897</v>
       </c>
       <c r="D303">
-        <v>66785</v>
+        <v>66791</v>
       </c>
       <c r="E303">
-        <v>81134</v>
+        <v>81146</v>
       </c>
     </row>
     <row r="304" spans="1:5">
@@ -5519,16 +5519,16 @@
         <v>303</v>
       </c>
       <c r="B304">
-        <v>17726</v>
+        <v>17741</v>
       </c>
       <c r="C304">
-        <v>30286</v>
+        <v>30300</v>
       </c>
       <c r="D304">
-        <v>53762</v>
+        <v>53805</v>
       </c>
       <c r="E304">
-        <v>69619</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="305" spans="1:5">
@@ -5536,16 +5536,16 @@
         <v>304</v>
       </c>
       <c r="B305">
-        <v>17726</v>
+        <v>17741</v>
       </c>
       <c r="C305">
-        <v>30286</v>
+        <v>30300</v>
       </c>
       <c r="D305">
-        <v>53762</v>
+        <v>53805</v>
       </c>
       <c r="E305">
-        <v>69619</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="306" spans="1:5">
@@ -5553,16 +5553,16 @@
         <v>305</v>
       </c>
       <c r="B306">
-        <v>15650</v>
+        <v>15661</v>
       </c>
       <c r="C306">
-        <v>27129</v>
+        <v>27142</v>
       </c>
       <c r="D306">
-        <v>49960</v>
+        <v>49982</v>
       </c>
       <c r="E306">
-        <v>66147</v>
+        <v>66185</v>
       </c>
     </row>
     <row r="307" spans="1:5">
@@ -5570,16 +5570,16 @@
         <v>306</v>
       </c>
       <c r="B307">
-        <v>17726</v>
+        <v>17741</v>
       </c>
       <c r="C307">
-        <v>30286</v>
+        <v>30300</v>
       </c>
       <c r="D307">
-        <v>53762</v>
+        <v>53805</v>
       </c>
       <c r="E307">
-        <v>69619</v>
+        <v>69674</v>
       </c>
     </row>
     <row r="308" spans="1:5">
@@ -5587,13 +5587,13 @@
         <v>307</v>
       </c>
       <c r="B308">
-        <v>20202</v>
+        <v>20203</v>
       </c>
       <c r="C308">
-        <v>34278</v>
+        <v>34279</v>
       </c>
       <c r="D308">
-        <v>58050</v>
+        <v>58052</v>
       </c>
       <c r="E308">
         <v>74576</v>
@@ -5604,16 +5604,16 @@
         <v>308</v>
       </c>
       <c r="B309">
-        <v>15650</v>
+        <v>15661</v>
       </c>
       <c r="C309">
-        <v>27129</v>
+        <v>27142</v>
       </c>
       <c r="D309">
-        <v>49960</v>
+        <v>49982</v>
       </c>
       <c r="E309">
-        <v>66147</v>
+        <v>66185</v>
       </c>
     </row>
     <row r="310" spans="1:5">
@@ -5621,13 +5621,13 @@
         <v>309</v>
       </c>
       <c r="B310">
-        <v>22790</v>
+        <v>22793</v>
       </c>
       <c r="C310">
-        <v>37919</v>
+        <v>37921</v>
       </c>
       <c r="D310">
-        <v>61987</v>
+        <v>61996</v>
       </c>
       <c r="E310">
         <v>77738</v>
@@ -5638,16 +5638,16 @@
         <v>310</v>
       </c>
       <c r="B311">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="C311">
-        <v>18816</v>
+        <v>18817</v>
       </c>
       <c r="D311">
-        <v>43840</v>
+        <v>43841</v>
       </c>
       <c r="E311">
-        <v>62709</v>
+        <v>62716</v>
       </c>
     </row>
     <row r="312" spans="1:5">
@@ -5655,16 +5655,16 @@
         <v>311</v>
       </c>
       <c r="B312">
-        <v>7348</v>
+        <v>7349</v>
       </c>
       <c r="C312">
-        <v>14356</v>
+        <v>14357</v>
       </c>
       <c r="D312">
-        <v>32272</v>
+        <v>32276</v>
       </c>
       <c r="E312">
-        <v>46278</v>
+        <v>46352</v>
       </c>
     </row>
     <row r="313" spans="1:5">
@@ -5672,16 +5672,16 @@
         <v>312</v>
       </c>
       <c r="B313">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="C313">
-        <v>18816</v>
+        <v>18817</v>
       </c>
       <c r="D313">
-        <v>43840</v>
+        <v>43841</v>
       </c>
       <c r="E313">
-        <v>62709</v>
+        <v>62716</v>
       </c>
     </row>
     <row r="314" spans="1:5">
@@ -5689,16 +5689,16 @@
         <v>313</v>
       </c>
       <c r="B314">
-        <v>9131</v>
+        <v>9132</v>
       </c>
       <c r="C314">
-        <v>18816</v>
+        <v>18817</v>
       </c>
       <c r="D314">
-        <v>43840</v>
+        <v>43841</v>
       </c>
       <c r="E314">
-        <v>62709</v>
+        <v>62716</v>
       </c>
     </row>
     <row r="315" spans="1:5">
@@ -5706,16 +5706,16 @@
         <v>314</v>
       </c>
       <c r="B315">
-        <v>31899</v>
+        <v>31975</v>
       </c>
       <c r="C315">
-        <v>46482</v>
+        <v>46598</v>
       </c>
       <c r="D315">
-        <v>67015</v>
+        <v>67125</v>
       </c>
       <c r="E315">
-        <v>79699</v>
+        <v>79749</v>
       </c>
     </row>
     <row r="316" spans="1:5">
@@ -5723,16 +5723,16 @@
         <v>315</v>
       </c>
       <c r="B316">
-        <v>36638</v>
+        <v>36794</v>
       </c>
       <c r="C316">
-        <v>48880</v>
+        <v>49059</v>
       </c>
       <c r="D316">
-        <v>66729</v>
+        <v>66894</v>
       </c>
       <c r="E316">
-        <v>79266</v>
+        <v>79375</v>
       </c>
     </row>
     <row r="317" spans="1:5">
@@ -5740,16 +5740,16 @@
         <v>316</v>
       </c>
       <c r="B317">
-        <v>34454</v>
+        <v>34592</v>
       </c>
       <c r="C317">
-        <v>46636</v>
+        <v>46858</v>
       </c>
       <c r="D317">
-        <v>64889</v>
+        <v>65122</v>
       </c>
       <c r="E317">
-        <v>77655</v>
+        <v>77789</v>
       </c>
     </row>
     <row r="318" spans="1:5">
@@ -5757,16 +5757,16 @@
         <v>317</v>
       </c>
       <c r="B318">
-        <v>32739</v>
+        <v>32807</v>
       </c>
       <c r="C318">
-        <v>45066</v>
+        <v>45189</v>
       </c>
       <c r="D318">
-        <v>63833</v>
+        <v>64037</v>
       </c>
       <c r="E318">
-        <v>77110</v>
+        <v>77242</v>
       </c>
     </row>
     <row r="319" spans="1:5">
@@ -5774,16 +5774,16 @@
         <v>318</v>
       </c>
       <c r="B319">
-        <v>25716</v>
+        <v>25778</v>
       </c>
       <c r="C319">
-        <v>38866</v>
+        <v>39040</v>
       </c>
       <c r="D319">
-        <v>59081</v>
+        <v>59343</v>
       </c>
       <c r="E319">
-        <v>73045</v>
+        <v>73209</v>
       </c>
     </row>
     <row r="320" spans="1:5">
@@ -5791,16 +5791,16 @@
         <v>319</v>
       </c>
       <c r="B320">
-        <v>29904</v>
+        <v>29958</v>
       </c>
       <c r="C320">
-        <v>42186</v>
+        <v>42341</v>
       </c>
       <c r="D320">
-        <v>61342</v>
+        <v>61608</v>
       </c>
       <c r="E320">
-        <v>74897</v>
+        <v>75054</v>
       </c>
     </row>
     <row r="321" spans="1:5">
@@ -5808,16 +5808,16 @@
         <v>320</v>
       </c>
       <c r="B321">
-        <v>32409</v>
+        <v>32500</v>
       </c>
       <c r="C321">
-        <v>44581</v>
+        <v>44752</v>
       </c>
       <c r="D321">
-        <v>63333</v>
+        <v>63565</v>
       </c>
       <c r="E321">
-        <v>76565</v>
+        <v>76703</v>
       </c>
     </row>
     <row r="322" spans="1:5">
@@ -5825,16 +5825,16 @@
         <v>321</v>
       </c>
       <c r="B322">
-        <v>37814</v>
+        <v>37820</v>
       </c>
       <c r="C322">
-        <v>53602</v>
+        <v>53618</v>
       </c>
       <c r="D322">
-        <v>73738</v>
+        <v>73758</v>
       </c>
       <c r="E322">
-        <v>85198</v>
+        <v>85211</v>
       </c>
     </row>
     <row r="323" spans="1:5">
@@ -5842,16 +5842,16 @@
         <v>322</v>
       </c>
       <c r="B323">
-        <v>31251</v>
+        <v>31303</v>
       </c>
       <c r="C323">
-        <v>42798</v>
+        <v>42907</v>
       </c>
       <c r="D323">
-        <v>61169</v>
+        <v>61354</v>
       </c>
       <c r="E323">
-        <v>74505</v>
+        <v>74643</v>
       </c>
     </row>
     <row r="324" spans="1:5">
@@ -5859,16 +5859,16 @@
         <v>323</v>
       </c>
       <c r="B324">
-        <v>31251</v>
+        <v>31303</v>
       </c>
       <c r="C324">
-        <v>42798</v>
+        <v>42907</v>
       </c>
       <c r="D324">
-        <v>61169</v>
+        <v>61354</v>
       </c>
       <c r="E324">
-        <v>74505</v>
+        <v>74643</v>
       </c>
     </row>
     <row r="325" spans="1:5">
@@ -5876,16 +5876,16 @@
         <v>324</v>
       </c>
       <c r="B325">
-        <v>31251</v>
+        <v>31303</v>
       </c>
       <c r="C325">
-        <v>42798</v>
+        <v>42907</v>
       </c>
       <c r="D325">
-        <v>61169</v>
+        <v>61354</v>
       </c>
       <c r="E325">
-        <v>74505</v>
+        <v>74643</v>
       </c>
     </row>
     <row r="326" spans="1:5">
@@ -5893,16 +5893,16 @@
         <v>325</v>
       </c>
       <c r="B326">
-        <v>34800</v>
+        <v>34862</v>
       </c>
       <c r="C326">
-        <v>46500</v>
+        <v>46652</v>
       </c>
       <c r="D326">
-        <v>64522</v>
+        <v>64724</v>
       </c>
       <c r="E326">
-        <v>77345</v>
+        <v>77486</v>
       </c>
     </row>
     <row r="327" spans="1:5">
@@ -5910,13 +5910,13 @@
         <v>326</v>
       </c>
       <c r="B327">
-        <v>32677</v>
+        <v>32684</v>
       </c>
       <c r="C327">
-        <v>48998</v>
+        <v>49022</v>
       </c>
       <c r="D327">
-        <v>69768</v>
+        <v>69794</v>
       </c>
       <c r="E327">
         <v>82610</v>
@@ -5927,16 +5927,16 @@
         <v>327</v>
       </c>
       <c r="B328">
-        <v>34221</v>
+        <v>34228</v>
       </c>
       <c r="C328">
-        <v>50761</v>
+        <v>50783</v>
       </c>
       <c r="D328">
-        <v>71813</v>
+        <v>71842</v>
       </c>
       <c r="E328">
-        <v>83476</v>
+        <v>83493</v>
       </c>
     </row>
     <row r="329" spans="1:5">
@@ -5944,16 +5944,16 @@
         <v>328</v>
       </c>
       <c r="B329">
-        <v>31565</v>
+        <v>31575</v>
       </c>
       <c r="C329">
-        <v>48356</v>
+        <v>48368</v>
       </c>
       <c r="D329">
-        <v>70284</v>
+        <v>70312</v>
       </c>
       <c r="E329">
-        <v>82484</v>
+        <v>82503</v>
       </c>
     </row>
     <row r="330" spans="1:5">
@@ -5961,16 +5961,16 @@
         <v>329</v>
       </c>
       <c r="B330">
-        <v>34221</v>
+        <v>34228</v>
       </c>
       <c r="C330">
-        <v>50761</v>
+        <v>50783</v>
       </c>
       <c r="D330">
-        <v>71813</v>
+        <v>71842</v>
       </c>
       <c r="E330">
-        <v>83476</v>
+        <v>83493</v>
       </c>
     </row>
     <row r="331" spans="1:5">
@@ -5978,16 +5978,16 @@
         <v>330</v>
       </c>
       <c r="B331">
-        <v>26246</v>
+        <v>26286</v>
       </c>
       <c r="C331">
-        <v>41135</v>
+        <v>41232</v>
       </c>
       <c r="D331">
-        <v>62969</v>
+        <v>63115</v>
       </c>
       <c r="E331">
-        <v>76274</v>
+        <v>76341</v>
       </c>
     </row>
     <row r="332" spans="1:5">
@@ -5995,16 +5995,16 @@
         <v>331</v>
       </c>
       <c r="B332">
-        <v>35717</v>
+        <v>35747</v>
       </c>
       <c r="C332">
-        <v>52133</v>
+        <v>52161</v>
       </c>
       <c r="D332">
-        <v>73033</v>
+        <v>73054</v>
       </c>
       <c r="E332">
-        <v>85409</v>
+        <v>85410</v>
       </c>
     </row>
     <row r="333" spans="1:5">
@@ -6012,16 +6012,16 @@
         <v>332</v>
       </c>
       <c r="B333">
-        <v>33414</v>
+        <v>33433</v>
       </c>
       <c r="C333">
-        <v>48315</v>
+        <v>48371</v>
       </c>
       <c r="D333">
-        <v>69947</v>
+        <v>70046</v>
       </c>
       <c r="E333">
-        <v>82572</v>
+        <v>82625</v>
       </c>
     </row>
     <row r="334" spans="1:5">
@@ -6029,13 +6029,13 @@
         <v>333</v>
       </c>
       <c r="B334">
-        <v>40769</v>
+        <v>40817</v>
       </c>
       <c r="C334">
-        <v>57788</v>
+        <v>57828</v>
       </c>
       <c r="D334">
-        <v>77765</v>
+        <v>77782</v>
       </c>
       <c r="E334">
         <v>88843</v>
@@ -6046,13 +6046,13 @@
         <v>334</v>
       </c>
       <c r="B335">
-        <v>38615</v>
+        <v>38634</v>
       </c>
       <c r="C335">
-        <v>55696</v>
+        <v>55721</v>
       </c>
       <c r="D335">
-        <v>76422</v>
+        <v>76439</v>
       </c>
       <c r="E335">
         <v>88052</v>
@@ -6063,16 +6063,16 @@
         <v>335</v>
       </c>
       <c r="B336">
-        <v>34591</v>
+        <v>34617</v>
       </c>
       <c r="C336">
-        <v>51117</v>
+        <v>51146</v>
       </c>
       <c r="D336">
-        <v>72799</v>
+        <v>72827</v>
       </c>
       <c r="E336">
-        <v>84504</v>
+        <v>84519</v>
       </c>
     </row>
     <row r="337" spans="1:5">
@@ -6080,16 +6080,16 @@
         <v>336</v>
       </c>
       <c r="B337">
-        <v>10266</v>
+        <v>10276</v>
       </c>
       <c r="C337">
-        <v>16084</v>
+        <v>16096</v>
       </c>
       <c r="D337">
-        <v>32937</v>
+        <v>32960</v>
       </c>
       <c r="E337">
-        <v>47587</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="338" spans="1:5">
@@ -6097,16 +6097,16 @@
         <v>337</v>
       </c>
       <c r="B338">
-        <v>10445</v>
+        <v>10448</v>
       </c>
       <c r="C338">
-        <v>16082</v>
+        <v>16085</v>
       </c>
       <c r="D338">
-        <v>32443</v>
+        <v>32450</v>
       </c>
       <c r="E338">
-        <v>46763</v>
+        <v>46772</v>
       </c>
     </row>
     <row r="339" spans="1:5">
@@ -6114,16 +6114,16 @@
         <v>338</v>
       </c>
       <c r="B339">
-        <v>10266</v>
+        <v>10276</v>
       </c>
       <c r="C339">
-        <v>16084</v>
+        <v>16096</v>
       </c>
       <c r="D339">
-        <v>32937</v>
+        <v>32960</v>
       </c>
       <c r="E339">
-        <v>47587</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="340" spans="1:5">
@@ -6131,16 +6131,16 @@
         <v>339</v>
       </c>
       <c r="B340">
-        <v>10730</v>
+        <v>10733</v>
       </c>
       <c r="C340">
-        <v>17155</v>
+        <v>17156</v>
       </c>
       <c r="D340">
-        <v>35579</v>
+        <v>35580</v>
       </c>
       <c r="E340">
-        <v>51782</v>
+        <v>51784</v>
       </c>
     </row>
     <row r="341" spans="1:5">
@@ -6148,13 +6148,13 @@
         <v>340</v>
       </c>
       <c r="B341">
-        <v>10428</v>
+        <v>10432</v>
       </c>
       <c r="C341">
-        <v>16685</v>
+        <v>16687</v>
       </c>
       <c r="D341">
-        <v>34562</v>
+        <v>34563</v>
       </c>
       <c r="E341">
         <v>51056</v>
@@ -6165,16 +6165,16 @@
         <v>341</v>
       </c>
       <c r="B342">
-        <v>12963</v>
+        <v>12985</v>
       </c>
       <c r="C342">
-        <v>20217</v>
+        <v>20229</v>
       </c>
       <c r="D342">
-        <v>40614</v>
+        <v>40624</v>
       </c>
       <c r="E342">
-        <v>57852</v>
+        <v>57862</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -6182,16 +6182,16 @@
         <v>342</v>
       </c>
       <c r="B343">
-        <v>12963</v>
+        <v>12985</v>
       </c>
       <c r="C343">
-        <v>20217</v>
+        <v>20229</v>
       </c>
       <c r="D343">
-        <v>40614</v>
+        <v>40624</v>
       </c>
       <c r="E343">
-        <v>57852</v>
+        <v>57862</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -6199,16 +6199,16 @@
         <v>343</v>
       </c>
       <c r="B344">
-        <v>10730</v>
+        <v>10733</v>
       </c>
       <c r="C344">
-        <v>17155</v>
+        <v>17156</v>
       </c>
       <c r="D344">
-        <v>35579</v>
+        <v>35580</v>
       </c>
       <c r="E344">
-        <v>51782</v>
+        <v>51784</v>
       </c>
     </row>
     <row r="345" spans="1:5">
@@ -6216,16 +6216,16 @@
         <v>344</v>
       </c>
       <c r="B345">
-        <v>7722</v>
+        <v>7724</v>
       </c>
       <c r="C345">
         <v>13422</v>
       </c>
       <c r="D345">
-        <v>30513</v>
+        <v>30514</v>
       </c>
       <c r="E345">
-        <v>45566</v>
+        <v>45568</v>
       </c>
     </row>
     <row r="346" spans="1:5">
@@ -6233,16 +6233,16 @@
         <v>345</v>
       </c>
       <c r="B346">
-        <v>7722</v>
+        <v>7724</v>
       </c>
       <c r="C346">
         <v>13422</v>
       </c>
       <c r="D346">
-        <v>30513</v>
+        <v>30514</v>
       </c>
       <c r="E346">
-        <v>45566</v>
+        <v>45568</v>
       </c>
     </row>
     <row r="347" spans="1:5">
@@ -6250,16 +6250,16 @@
         <v>346</v>
       </c>
       <c r="B347">
-        <v>7722</v>
+        <v>7724</v>
       </c>
       <c r="C347">
         <v>13422</v>
       </c>
       <c r="D347">
-        <v>30513</v>
+        <v>30514</v>
       </c>
       <c r="E347">
-        <v>45566</v>
+        <v>45568</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -6267,16 +6267,16 @@
         <v>347</v>
       </c>
       <c r="B348">
-        <v>12161</v>
+        <v>12172</v>
       </c>
       <c r="C348">
-        <v>18908</v>
+        <v>18916</v>
       </c>
       <c r="D348">
-        <v>37506</v>
+        <v>37513</v>
       </c>
       <c r="E348">
-        <v>53723</v>
+        <v>53728</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -6284,16 +6284,16 @@
         <v>348</v>
       </c>
       <c r="B349">
-        <v>12161</v>
+        <v>12172</v>
       </c>
       <c r="C349">
-        <v>18908</v>
+        <v>18916</v>
       </c>
       <c r="D349">
-        <v>37506</v>
+        <v>37513</v>
       </c>
       <c r="E349">
-        <v>53723</v>
+        <v>53728</v>
       </c>
     </row>
     <row r="350" spans="1:5">
@@ -6301,16 +6301,16 @@
         <v>349</v>
       </c>
       <c r="B350">
-        <v>12161</v>
+        <v>12172</v>
       </c>
       <c r="C350">
-        <v>18908</v>
+        <v>18916</v>
       </c>
       <c r="D350">
-        <v>37506</v>
+        <v>37513</v>
       </c>
       <c r="E350">
-        <v>53723</v>
+        <v>53728</v>
       </c>
     </row>
     <row r="351" spans="1:5">
@@ -6318,16 +6318,16 @@
         <v>350</v>
       </c>
       <c r="B351">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="C351">
-        <v>11794</v>
+        <v>11798</v>
       </c>
       <c r="D351">
-        <v>27888</v>
+        <v>27890</v>
       </c>
       <c r="E351">
-        <v>41171</v>
+        <v>41175</v>
       </c>
     </row>
     <row r="352" spans="1:5">
@@ -6335,16 +6335,16 @@
         <v>351</v>
       </c>
       <c r="B352">
-        <v>6417</v>
+        <v>6425</v>
       </c>
       <c r="C352">
-        <v>11794</v>
+        <v>11798</v>
       </c>
       <c r="D352">
-        <v>27888</v>
+        <v>27890</v>
       </c>
       <c r="E352">
-        <v>41171</v>
+        <v>41175</v>
       </c>
     </row>
     <row r="353" spans="1:5">
@@ -6352,13 +6352,13 @@
         <v>352</v>
       </c>
       <c r="B353">
-        <v>16759</v>
+        <v>16763</v>
       </c>
       <c r="C353">
-        <v>24887</v>
+        <v>24893</v>
       </c>
       <c r="D353">
-        <v>47078</v>
+        <v>47082</v>
       </c>
       <c r="E353">
         <v>65634</v>
@@ -6369,16 +6369,16 @@
         <v>353</v>
       </c>
       <c r="B354">
-        <v>14397</v>
+        <v>14400</v>
       </c>
       <c r="C354">
-        <v>21018</v>
+        <v>21021</v>
       </c>
       <c r="D354">
-        <v>40716</v>
+        <v>40717</v>
       </c>
       <c r="E354">
-        <v>58004</v>
+        <v>58010</v>
       </c>
     </row>
     <row r="355" spans="1:5">
@@ -6386,16 +6386,16 @@
         <v>354</v>
       </c>
       <c r="B355">
-        <v>17403</v>
+        <v>17407</v>
       </c>
       <c r="C355">
-        <v>25863</v>
+        <v>25869</v>
       </c>
       <c r="D355">
-        <v>48831</v>
+        <v>48835</v>
       </c>
       <c r="E355">
-        <v>66652</v>
+        <v>66662</v>
       </c>
     </row>
     <row r="356" spans="1:5">
@@ -6403,16 +6403,16 @@
         <v>355</v>
       </c>
       <c r="B356">
-        <v>12902</v>
+        <v>12903</v>
       </c>
       <c r="C356">
-        <v>18965</v>
+        <v>18966</v>
       </c>
       <c r="D356">
-        <v>36868</v>
+        <v>36869</v>
       </c>
       <c r="E356">
-        <v>53550</v>
+        <v>53553</v>
       </c>
     </row>
     <row r="357" spans="1:5">
@@ -6420,16 +6420,16 @@
         <v>356</v>
       </c>
       <c r="B357">
-        <v>12902</v>
+        <v>12903</v>
       </c>
       <c r="C357">
-        <v>18965</v>
+        <v>18966</v>
       </c>
       <c r="D357">
-        <v>36868</v>
+        <v>36869</v>
       </c>
       <c r="E357">
-        <v>53550</v>
+        <v>53553</v>
       </c>
     </row>
     <row r="358" spans="1:5">
@@ -6437,16 +6437,16 @@
         <v>357</v>
       </c>
       <c r="B358">
-        <v>12902</v>
+        <v>12903</v>
       </c>
       <c r="C358">
-        <v>18965</v>
+        <v>18966</v>
       </c>
       <c r="D358">
-        <v>36868</v>
+        <v>36869</v>
       </c>
       <c r="E358">
-        <v>53550</v>
+        <v>53553</v>
       </c>
     </row>
     <row r="359" spans="1:5">
@@ -6454,16 +6454,16 @@
         <v>358</v>
       </c>
       <c r="B359">
-        <v>6421</v>
+        <v>6437</v>
       </c>
       <c r="C359">
-        <v>12115</v>
+        <v>12124</v>
       </c>
       <c r="D359">
-        <v>28653</v>
+        <v>28657</v>
       </c>
       <c r="E359">
-        <v>42724</v>
+        <v>42726</v>
       </c>
     </row>
     <row r="360" spans="1:5">
@@ -6471,16 +6471,16 @@
         <v>359</v>
       </c>
       <c r="B360">
-        <v>6421</v>
+        <v>6437</v>
       </c>
       <c r="C360">
-        <v>12115</v>
+        <v>12124</v>
       </c>
       <c r="D360">
-        <v>28653</v>
+        <v>28657</v>
       </c>
       <c r="E360">
-        <v>42724</v>
+        <v>42726</v>
       </c>
     </row>
     <row r="361" spans="1:5">
@@ -6488,13 +6488,13 @@
         <v>360</v>
       </c>
       <c r="B361">
-        <v>21985</v>
+        <v>21989</v>
       </c>
       <c r="C361">
-        <v>39030</v>
+        <v>39032</v>
       </c>
       <c r="D361">
-        <v>65762</v>
+        <v>65772</v>
       </c>
       <c r="E361">
         <v>81682</v>
@@ -6505,16 +6505,16 @@
         <v>361</v>
       </c>
       <c r="B362">
-        <v>20375</v>
+        <v>20377</v>
       </c>
       <c r="C362">
-        <v>37997</v>
+        <v>37999</v>
       </c>
       <c r="D362">
-        <v>66120</v>
+        <v>66140</v>
       </c>
       <c r="E362">
-        <v>81376</v>
+        <v>81399</v>
       </c>
     </row>
     <row r="363" spans="1:5">
@@ -6522,16 +6522,16 @@
         <v>362</v>
       </c>
       <c r="B363">
-        <v>15966</v>
+        <v>15967</v>
       </c>
       <c r="C363">
-        <v>32295</v>
+        <v>32296</v>
       </c>
       <c r="D363">
-        <v>61541</v>
+        <v>61553</v>
       </c>
       <c r="E363">
-        <v>78488</v>
+        <v>78509</v>
       </c>
     </row>
     <row r="364" spans="1:5">
@@ -6545,10 +6545,10 @@
         <v>40600</v>
       </c>
       <c r="D364">
-        <v>66584</v>
+        <v>66585</v>
       </c>
       <c r="E364">
-        <v>81803</v>
+        <v>81811</v>
       </c>
     </row>
     <row r="365" spans="1:5">
@@ -6562,10 +6562,10 @@
         <v>40600</v>
       </c>
       <c r="D365">
-        <v>66584</v>
+        <v>66585</v>
       </c>
       <c r="E365">
-        <v>81803</v>
+        <v>81811</v>
       </c>
     </row>
     <row r="366" spans="1:5">
@@ -6573,16 +6573,16 @@
         <v>365</v>
       </c>
       <c r="B366">
-        <v>17892</v>
+        <v>17894</v>
       </c>
       <c r="C366">
-        <v>33241</v>
+        <v>33242</v>
       </c>
       <c r="D366">
-        <v>60707</v>
+        <v>60712</v>
       </c>
       <c r="E366">
-        <v>77552</v>
+        <v>77570</v>
       </c>
     </row>
     <row r="367" spans="1:5">
@@ -6590,16 +6590,16 @@
         <v>366</v>
       </c>
       <c r="B367">
-        <v>17892</v>
+        <v>17894</v>
       </c>
       <c r="C367">
-        <v>33241</v>
+        <v>33242</v>
       </c>
       <c r="D367">
-        <v>60707</v>
+        <v>60712</v>
       </c>
       <c r="E367">
-        <v>77552</v>
+        <v>77570</v>
       </c>
     </row>
     <row r="368" spans="1:5">
@@ -6613,10 +6613,10 @@
         <v>34846</v>
       </c>
       <c r="D368">
-        <v>61638</v>
+        <v>61639</v>
       </c>
       <c r="E368">
-        <v>78265</v>
+        <v>78274</v>
       </c>
     </row>
     <row r="369" spans="1:5">
@@ -6624,16 +6624,16 @@
         <v>368</v>
       </c>
       <c r="B369">
-        <v>17892</v>
+        <v>17894</v>
       </c>
       <c r="C369">
-        <v>33241</v>
+        <v>33242</v>
       </c>
       <c r="D369">
-        <v>60707</v>
+        <v>60712</v>
       </c>
       <c r="E369">
-        <v>77552</v>
+        <v>77570</v>
       </c>
     </row>
     <row r="370" spans="1:5">
@@ -6641,16 +6641,16 @@
         <v>369</v>
       </c>
       <c r="B370">
-        <v>11956</v>
+        <v>11963</v>
       </c>
       <c r="C370">
-        <v>26180</v>
+        <v>26185</v>
       </c>
       <c r="D370">
-        <v>55329</v>
+        <v>55344</v>
       </c>
       <c r="E370">
-        <v>73749</v>
+        <v>73771</v>
       </c>
     </row>
     <row r="371" spans="1:5">
@@ -6658,16 +6658,16 @@
         <v>370</v>
       </c>
       <c r="B371">
-        <v>11956</v>
+        <v>11963</v>
       </c>
       <c r="C371">
-        <v>26180</v>
+        <v>26185</v>
       </c>
       <c r="D371">
-        <v>55329</v>
+        <v>55344</v>
       </c>
       <c r="E371">
-        <v>73749</v>
+        <v>73771</v>
       </c>
     </row>
     <row r="372" spans="1:5">
@@ -6675,16 +6675,16 @@
         <v>371</v>
       </c>
       <c r="B372">
-        <v>11956</v>
+        <v>11963</v>
       </c>
       <c r="C372">
-        <v>26180</v>
+        <v>26185</v>
       </c>
       <c r="D372">
-        <v>55329</v>
+        <v>55344</v>
       </c>
       <c r="E372">
-        <v>73749</v>
+        <v>73771</v>
       </c>
     </row>
     <row r="373" spans="1:5">
@@ -6692,13 +6692,13 @@
         <v>372</v>
       </c>
       <c r="B373">
-        <v>19418</v>
+        <v>19423</v>
       </c>
       <c r="C373">
-        <v>31758</v>
+        <v>31767</v>
       </c>
       <c r="D373">
-        <v>55401</v>
+        <v>55405</v>
       </c>
       <c r="E373">
         <v>71575</v>
@@ -6709,13 +6709,13 @@
         <v>373</v>
       </c>
       <c r="B374">
-        <v>14736</v>
+        <v>14737</v>
       </c>
       <c r="C374">
-        <v>23627</v>
+        <v>23631</v>
       </c>
       <c r="D374">
-        <v>46471</v>
+        <v>46475</v>
       </c>
       <c r="E374">
         <v>64978</v>
@@ -6726,16 +6726,16 @@
         <v>374</v>
       </c>
       <c r="B375">
-        <v>19813</v>
+        <v>19818</v>
       </c>
       <c r="C375">
-        <v>32717</v>
+        <v>32725</v>
       </c>
       <c r="D375">
-        <v>57221</v>
+        <v>57225</v>
       </c>
       <c r="E375">
-        <v>72483</v>
+        <v>72486</v>
       </c>
     </row>
     <row r="376" spans="1:5">
@@ -6743,16 +6743,16 @@
         <v>375</v>
       </c>
       <c r="B376">
-        <v>15570</v>
+        <v>15572</v>
       </c>
       <c r="C376">
-        <v>25167</v>
+        <v>25172</v>
       </c>
       <c r="D376">
-        <v>49265</v>
+        <v>49269</v>
       </c>
       <c r="E376">
-        <v>66969</v>
+        <v>66971</v>
       </c>
     </row>
     <row r="377" spans="1:5">
@@ -6760,16 +6760,16 @@
         <v>376</v>
       </c>
       <c r="B377">
-        <v>15570</v>
+        <v>15572</v>
       </c>
       <c r="C377">
-        <v>25167</v>
+        <v>25172</v>
       </c>
       <c r="D377">
-        <v>49265</v>
+        <v>49269</v>
       </c>
       <c r="E377">
-        <v>66969</v>
+        <v>66971</v>
       </c>
     </row>
     <row r="378" spans="1:5">
@@ -6777,13 +6777,13 @@
         <v>377</v>
       </c>
       <c r="B378">
-        <v>25028</v>
+        <v>25031</v>
       </c>
       <c r="C378">
-        <v>37816</v>
+        <v>37818</v>
       </c>
       <c r="D378">
-        <v>60789</v>
+        <v>60792</v>
       </c>
       <c r="E378">
         <v>76034</v>
@@ -6794,13 +6794,13 @@
         <v>378</v>
       </c>
       <c r="B379">
-        <v>25028</v>
+        <v>25031</v>
       </c>
       <c r="C379">
-        <v>37816</v>
+        <v>37818</v>
       </c>
       <c r="D379">
-        <v>60789</v>
+        <v>60792</v>
       </c>
       <c r="E379">
         <v>76034</v>
@@ -6811,16 +6811,16 @@
         <v>379</v>
       </c>
       <c r="B380">
-        <v>25022</v>
+        <v>25025</v>
       </c>
       <c r="C380">
-        <v>38780</v>
+        <v>38781</v>
       </c>
       <c r="D380">
-        <v>62735</v>
+        <v>62738</v>
       </c>
       <c r="E380">
-        <v>76934</v>
+        <v>76943</v>
       </c>
     </row>
     <row r="381" spans="1:5">
@@ -6828,16 +6828,16 @@
         <v>380</v>
       </c>
       <c r="B381">
-        <v>25022</v>
+        <v>25025</v>
       </c>
       <c r="C381">
-        <v>38780</v>
+        <v>38781</v>
       </c>
       <c r="D381">
-        <v>62735</v>
+        <v>62738</v>
       </c>
       <c r="E381">
-        <v>76934</v>
+        <v>76943</v>
       </c>
     </row>
     <row r="382" spans="1:5">
@@ -6845,16 +6845,16 @@
         <v>381</v>
       </c>
       <c r="B382">
-        <v>20123</v>
+        <v>20124</v>
       </c>
       <c r="C382">
-        <v>32664</v>
+        <v>32669</v>
       </c>
       <c r="D382">
-        <v>57801</v>
+        <v>57804</v>
       </c>
       <c r="E382">
-        <v>73618</v>
+        <v>73636</v>
       </c>
     </row>
     <row r="383" spans="1:5">
@@ -6862,16 +6862,16 @@
         <v>382</v>
       </c>
       <c r="B383">
-        <v>24685</v>
+        <v>24686</v>
       </c>
       <c r="C383">
-        <v>41019</v>
+        <v>41020</v>
       </c>
       <c r="D383">
-        <v>65233</v>
+        <v>65238</v>
       </c>
       <c r="E383">
-        <v>78771</v>
+        <v>78790</v>
       </c>
     </row>
     <row r="384" spans="1:5">
@@ -6879,16 +6879,16 @@
         <v>383</v>
       </c>
       <c r="B384">
-        <v>19818</v>
+        <v>19822</v>
       </c>
       <c r="C384">
-        <v>34329</v>
+        <v>34330</v>
       </c>
       <c r="D384">
-        <v>59694</v>
+        <v>59696</v>
       </c>
       <c r="E384">
-        <v>74872</v>
+        <v>74877</v>
       </c>
     </row>
     <row r="385" spans="1:5">
@@ -6896,16 +6896,16 @@
         <v>384</v>
       </c>
       <c r="B385">
-        <v>32044</v>
+        <v>32046</v>
       </c>
       <c r="C385">
-        <v>48813</v>
+        <v>48816</v>
       </c>
       <c r="D385">
-        <v>70782</v>
+        <v>70789</v>
       </c>
       <c r="E385">
-        <v>82781</v>
+        <v>82793</v>
       </c>
     </row>
     <row r="386" spans="1:5">
@@ -6913,16 +6913,16 @@
         <v>385</v>
       </c>
       <c r="B386">
-        <v>15802</v>
+        <v>15803</v>
       </c>
       <c r="C386">
         <v>28808</v>
       </c>
       <c r="D386">
-        <v>54661</v>
+        <v>54664</v>
       </c>
       <c r="E386">
-        <v>71478</v>
+        <v>71489</v>
       </c>
     </row>
     <row r="387" spans="1:5">
@@ -6930,16 +6930,16 @@
         <v>386</v>
       </c>
       <c r="B387">
-        <v>15802</v>
+        <v>15803</v>
       </c>
       <c r="C387">
         <v>28808</v>
       </c>
       <c r="D387">
-        <v>54661</v>
+        <v>54664</v>
       </c>
       <c r="E387">
-        <v>71478</v>
+        <v>71489</v>
       </c>
     </row>
     <row r="388" spans="1:5">
@@ -6947,16 +6947,16 @@
         <v>387</v>
       </c>
       <c r="B388">
-        <v>7517</v>
+        <v>7529</v>
       </c>
       <c r="C388">
-        <v>11682</v>
+        <v>11687</v>
       </c>
       <c r="D388">
-        <v>31474</v>
+        <v>31476</v>
       </c>
       <c r="E388">
-        <v>51234</v>
+        <v>51235</v>
       </c>
     </row>
     <row r="389" spans="1:5">
@@ -6964,16 +6964,16 @@
         <v>388</v>
       </c>
       <c r="B389">
-        <v>5732</v>
+        <v>5786</v>
       </c>
       <c r="C389">
-        <v>9928</v>
+        <v>9955</v>
       </c>
       <c r="D389">
-        <v>30498</v>
+        <v>30509</v>
       </c>
       <c r="E389">
-        <v>50960</v>
+        <v>50971</v>
       </c>
     </row>
     <row r="390" spans="1:5">
@@ -6981,16 +6981,16 @@
         <v>389</v>
       </c>
       <c r="B390">
-        <v>5732</v>
+        <v>5786</v>
       </c>
       <c r="C390">
-        <v>9928</v>
+        <v>9955</v>
       </c>
       <c r="D390">
-        <v>30498</v>
+        <v>30509</v>
       </c>
       <c r="E390">
-        <v>50960</v>
+        <v>50971</v>
       </c>
     </row>
     <row r="391" spans="1:5">
@@ -6998,16 +6998,16 @@
         <v>390</v>
       </c>
       <c r="B391">
-        <v>7517</v>
+        <v>7529</v>
       </c>
       <c r="C391">
-        <v>11682</v>
+        <v>11687</v>
       </c>
       <c r="D391">
-        <v>31474</v>
+        <v>31476</v>
       </c>
       <c r="E391">
-        <v>51234</v>
+        <v>51235</v>
       </c>
     </row>
     <row r="392" spans="1:5">
@@ -7015,16 +7015,16 @@
         <v>391</v>
       </c>
       <c r="B392">
-        <v>5732</v>
+        <v>5786</v>
       </c>
       <c r="C392">
-        <v>9928</v>
+        <v>9955</v>
       </c>
       <c r="D392">
-        <v>30498</v>
+        <v>30509</v>
       </c>
       <c r="E392">
-        <v>50960</v>
+        <v>50971</v>
       </c>
     </row>
     <row r="393" spans="1:5">
@@ -7035,10 +7035,10 @@
         <v>4795</v>
       </c>
       <c r="C393">
-        <v>7775</v>
+        <v>7776</v>
       </c>
       <c r="D393">
-        <v>22816</v>
+        <v>22817</v>
       </c>
       <c r="E393">
         <v>38077</v>
@@ -7052,10 +7052,10 @@
         <v>4795</v>
       </c>
       <c r="C394">
-        <v>7775</v>
+        <v>7776</v>
       </c>
       <c r="D394">
-        <v>22816</v>
+        <v>22817</v>
       </c>
       <c r="E394">
         <v>38077</v>
@@ -7066,16 +7066,16 @@
         <v>394</v>
       </c>
       <c r="B395">
-        <v>4769</v>
+        <v>4770</v>
       </c>
       <c r="C395">
-        <v>8133</v>
+        <v>8134</v>
       </c>
       <c r="D395">
-        <v>23555</v>
+        <v>23556</v>
       </c>
       <c r="E395">
-        <v>38791</v>
+        <v>38792</v>
       </c>
     </row>
     <row r="396" spans="1:5">
@@ -7083,16 +7083,16 @@
         <v>395</v>
       </c>
       <c r="B396">
-        <v>4769</v>
+        <v>4770</v>
       </c>
       <c r="C396">
-        <v>8133</v>
+        <v>8134</v>
       </c>
       <c r="D396">
-        <v>23555</v>
+        <v>23556</v>
       </c>
       <c r="E396">
-        <v>38791</v>
+        <v>38792</v>
       </c>
     </row>
     <row r="397" spans="1:5">
@@ -7134,10 +7134,10 @@
         <v>398</v>
       </c>
       <c r="B399">
-        <v>3927</v>
+        <v>3930</v>
       </c>
       <c r="C399">
-        <v>9042</v>
+        <v>9043</v>
       </c>
       <c r="D399">
         <v>32367</v>
@@ -7151,16 +7151,16 @@
         <v>399</v>
       </c>
       <c r="B400">
-        <v>3770</v>
+        <v>3773</v>
       </c>
       <c r="C400">
-        <v>9066</v>
+        <v>9067</v>
       </c>
       <c r="D400">
-        <v>33271</v>
+        <v>33272</v>
       </c>
       <c r="E400">
-        <v>55697</v>
+        <v>55703</v>
       </c>
     </row>
     <row r="401" spans="1:5">
@@ -7168,16 +7168,16 @@
         <v>400</v>
       </c>
       <c r="B401">
-        <v>4054</v>
+        <v>4056</v>
       </c>
       <c r="C401">
-        <v>9542</v>
+        <v>9543</v>
       </c>
       <c r="D401">
         <v>33738</v>
       </c>
       <c r="E401">
-        <v>55867</v>
+        <v>55873</v>
       </c>
     </row>
     <row r="402" spans="1:5">
@@ -7185,16 +7185,16 @@
         <v>401</v>
       </c>
       <c r="B402">
-        <v>3252</v>
+        <v>3254</v>
       </c>
       <c r="C402">
-        <v>7794</v>
+        <v>7795</v>
       </c>
       <c r="D402">
-        <v>30220</v>
+        <v>30221</v>
       </c>
       <c r="E402">
-        <v>51697</v>
+        <v>51701</v>
       </c>
     </row>
     <row r="403" spans="1:5">
@@ -7202,16 +7202,16 @@
         <v>402</v>
       </c>
       <c r="B403">
-        <v>3770</v>
+        <v>3773</v>
       </c>
       <c r="C403">
-        <v>9066</v>
+        <v>9067</v>
       </c>
       <c r="D403">
-        <v>33271</v>
+        <v>33272</v>
       </c>
       <c r="E403">
-        <v>55697</v>
+        <v>55703</v>
       </c>
     </row>
     <row r="404" spans="1:5">
@@ -7219,7 +7219,7 @@
         <v>403</v>
       </c>
       <c r="B404">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="C404">
         <v>7320</v>
@@ -7228,7 +7228,7 @@
         <v>29244</v>
       </c>
       <c r="E404">
-        <v>50807</v>
+        <v>50810</v>
       </c>
     </row>
     <row r="405" spans="1:5">
@@ -7236,7 +7236,7 @@
         <v>404</v>
       </c>
       <c r="B405">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="C405">
         <v>7320</v>
@@ -7245,7 +7245,7 @@
         <v>29244</v>
       </c>
       <c r="E405">
-        <v>50807</v>
+        <v>50810</v>
       </c>
     </row>
     <row r="406" spans="1:5">
@@ -7253,7 +7253,7 @@
         <v>405</v>
       </c>
       <c r="B406">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="C406">
         <v>7320</v>
@@ -7262,7 +7262,7 @@
         <v>29244</v>
       </c>
       <c r="E406">
-        <v>50807</v>
+        <v>50810</v>
       </c>
     </row>
     <row r="407" spans="1:5">
@@ -7276,10 +7276,10 @@
         <v>6198</v>
       </c>
       <c r="D407">
-        <v>26544</v>
+        <v>26545</v>
       </c>
       <c r="E407">
-        <v>47366</v>
+        <v>47368</v>
       </c>
     </row>
     <row r="408" spans="1:5">
@@ -7293,10 +7293,10 @@
         <v>6198</v>
       </c>
       <c r="D408">
-        <v>26544</v>
+        <v>26545</v>
       </c>
       <c r="E408">
-        <v>47366</v>
+        <v>47368</v>
       </c>
     </row>
     <row r="409" spans="1:5">
@@ -7310,10 +7310,10 @@
         <v>6198</v>
       </c>
       <c r="D409">
-        <v>26544</v>
+        <v>26545</v>
       </c>
       <c r="E409">
-        <v>47366</v>
+        <v>47368</v>
       </c>
     </row>
     <row r="410" spans="1:5">
@@ -7321,13 +7321,13 @@
         <v>409</v>
       </c>
       <c r="B410">
-        <v>12358</v>
+        <v>12360</v>
       </c>
       <c r="C410">
         <v>25350</v>
       </c>
       <c r="D410">
-        <v>53665</v>
+        <v>53669</v>
       </c>
       <c r="E410">
         <v>73884</v>
@@ -7338,16 +7338,16 @@
         <v>410</v>
       </c>
       <c r="B411">
-        <v>9321</v>
+        <v>9328</v>
       </c>
       <c r="C411">
-        <v>20667</v>
+        <v>20669</v>
       </c>
       <c r="D411">
-        <v>49780</v>
+        <v>49783</v>
       </c>
       <c r="E411">
-        <v>70647</v>
+        <v>70662</v>
       </c>
     </row>
     <row r="412" spans="1:5">
@@ -7355,16 +7355,16 @@
         <v>411</v>
       </c>
       <c r="B412">
-        <v>9321</v>
+        <v>9328</v>
       </c>
       <c r="C412">
-        <v>20667</v>
+        <v>20669</v>
       </c>
       <c r="D412">
-        <v>49780</v>
+        <v>49783</v>
       </c>
       <c r="E412">
-        <v>70647</v>
+        <v>70662</v>
       </c>
     </row>
     <row r="413" spans="1:5">
@@ -7372,16 +7372,16 @@
         <v>412</v>
       </c>
       <c r="B413">
-        <v>8308</v>
+        <v>8312</v>
       </c>
       <c r="C413">
-        <v>19425</v>
+        <v>19427</v>
       </c>
       <c r="D413">
-        <v>48095</v>
+        <v>48100</v>
       </c>
       <c r="E413">
-        <v>68515</v>
+        <v>68531</v>
       </c>
     </row>
     <row r="414" spans="1:5">
@@ -7389,16 +7389,16 @@
         <v>413</v>
       </c>
       <c r="B414">
-        <v>12953</v>
+        <v>12955</v>
       </c>
       <c r="C414">
         <v>26666</v>
       </c>
       <c r="D414">
-        <v>55734</v>
+        <v>55739</v>
       </c>
       <c r="E414">
-        <v>74887</v>
+        <v>74908</v>
       </c>
     </row>
     <row r="415" spans="1:5">
@@ -7412,10 +7412,10 @@
         <v>21925</v>
       </c>
       <c r="D415">
-        <v>51006</v>
+        <v>51008</v>
       </c>
       <c r="E415">
-        <v>71502</v>
+        <v>71511</v>
       </c>
     </row>
     <row r="416" spans="1:5">
@@ -7429,10 +7429,10 @@
         <v>21925</v>
       </c>
       <c r="D416">
-        <v>51006</v>
+        <v>51008</v>
       </c>
       <c r="E416">
-        <v>71502</v>
+        <v>71511</v>
       </c>
     </row>
     <row r="417" spans="1:5">
@@ -7446,10 +7446,10 @@
         <v>14615</v>
       </c>
       <c r="D417">
-        <v>41609</v>
+        <v>41610</v>
       </c>
       <c r="E417">
-        <v>63236</v>
+        <v>63247</v>
       </c>
     </row>
     <row r="418" spans="1:5">
@@ -7463,10 +7463,10 @@
         <v>14615</v>
       </c>
       <c r="D418">
-        <v>41609</v>
+        <v>41610</v>
       </c>
       <c r="E418">
-        <v>63236</v>
+        <v>63247</v>
       </c>
     </row>
     <row r="419" spans="1:5">
@@ -7474,7 +7474,7 @@
         <v>418</v>
       </c>
       <c r="B419">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C419">
         <v>19576</v>
@@ -7491,7 +7491,7 @@
         <v>419</v>
       </c>
       <c r="B420">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C420">
         <v>19576</v>
@@ -7508,16 +7508,16 @@
         <v>420</v>
       </c>
       <c r="B421">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="C421">
-        <v>15346</v>
+        <v>15350</v>
       </c>
       <c r="D421">
-        <v>36579</v>
+        <v>36585</v>
       </c>
       <c r="E421">
-        <v>54676</v>
+        <v>54695</v>
       </c>
     </row>
     <row r="422" spans="1:5">
@@ -7525,16 +7525,16 @@
         <v>421</v>
       </c>
       <c r="B422">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="C422">
-        <v>15346</v>
+        <v>15350</v>
       </c>
       <c r="D422">
-        <v>36579</v>
+        <v>36585</v>
       </c>
       <c r="E422">
-        <v>54676</v>
+        <v>54695</v>
       </c>
     </row>
     <row r="423" spans="1:5">
@@ -7542,7 +7542,7 @@
         <v>422</v>
       </c>
       <c r="B423">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C423">
         <v>19576</v>
@@ -7559,7 +7559,7 @@
         <v>423</v>
       </c>
       <c r="B424">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C424">
         <v>19576</v>
@@ -7576,16 +7576,16 @@
         <v>424</v>
       </c>
       <c r="B425">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="C425">
-        <v>15346</v>
+        <v>15350</v>
       </c>
       <c r="D425">
-        <v>36579</v>
+        <v>36585</v>
       </c>
       <c r="E425">
-        <v>54676</v>
+        <v>54695</v>
       </c>
     </row>
     <row r="426" spans="1:5">
@@ -7593,7 +7593,7 @@
         <v>425</v>
       </c>
       <c r="B426">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C426">
         <v>19576</v>
@@ -7610,16 +7610,16 @@
         <v>426</v>
       </c>
       <c r="B427">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="C427">
-        <v>20338</v>
+        <v>20339</v>
       </c>
       <c r="D427">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="E427">
-        <v>64714</v>
+        <v>64718</v>
       </c>
     </row>
     <row r="428" spans="1:5">
@@ -7627,16 +7627,16 @@
         <v>427</v>
       </c>
       <c r="B428">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="C428">
-        <v>20338</v>
+        <v>20339</v>
       </c>
       <c r="D428">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="E428">
-        <v>64714</v>
+        <v>64718</v>
       </c>
     </row>
     <row r="429" spans="1:5">
@@ -7644,7 +7644,7 @@
         <v>428</v>
       </c>
       <c r="B429">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C429">
         <v>19576</v>
@@ -7661,7 +7661,7 @@
         <v>429</v>
       </c>
       <c r="B430">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C430">
         <v>19576</v>
@@ -7678,16 +7678,16 @@
         <v>430</v>
       </c>
       <c r="B431">
-        <v>8955</v>
+        <v>8962</v>
       </c>
       <c r="C431">
-        <v>15346</v>
+        <v>15350</v>
       </c>
       <c r="D431">
-        <v>36579</v>
+        <v>36585</v>
       </c>
       <c r="E431">
-        <v>54676</v>
+        <v>54695</v>
       </c>
     </row>
     <row r="432" spans="1:5">
@@ -7695,7 +7695,7 @@
         <v>431</v>
       </c>
       <c r="B432">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C432">
         <v>19576</v>
@@ -7712,7 +7712,7 @@
         <v>432</v>
       </c>
       <c r="B433">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C433">
         <v>19576</v>
@@ -7729,10 +7729,10 @@
         <v>433</v>
       </c>
       <c r="B434">
-        <v>7240</v>
+        <v>7245</v>
       </c>
       <c r="C434">
-        <v>13587</v>
+        <v>13589</v>
       </c>
       <c r="D434">
         <v>35027</v>
@@ -7746,7 +7746,7 @@
         <v>434</v>
       </c>
       <c r="B435">
-        <v>10930</v>
+        <v>10932</v>
       </c>
       <c r="C435">
         <v>19576</v>
@@ -7766,13 +7766,13 @@
         <v>6882</v>
       </c>
       <c r="C436">
-        <v>14068</v>
+        <v>14069</v>
       </c>
       <c r="D436">
         <v>36969</v>
       </c>
       <c r="E436">
-        <v>55978</v>
+        <v>55984</v>
       </c>
     </row>
     <row r="437" spans="1:5">
@@ -7789,7 +7789,7 @@
         <v>29042</v>
       </c>
       <c r="E437">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="438" spans="1:5">
@@ -7806,7 +7806,7 @@
         <v>29042</v>
       </c>
       <c r="E438">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="439" spans="1:5">
@@ -7823,7 +7823,7 @@
         <v>29042</v>
       </c>
       <c r="E439">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="440" spans="1:5">
@@ -7840,7 +7840,7 @@
         <v>29042</v>
       </c>
       <c r="E440">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="441" spans="1:5">
@@ -7857,7 +7857,7 @@
         <v>29042</v>
       </c>
       <c r="E441">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="442" spans="1:5">
@@ -7874,7 +7874,7 @@
         <v>27118</v>
       </c>
       <c r="E442">
-        <v>42970</v>
+        <v>42972</v>
       </c>
     </row>
     <row r="443" spans="1:5">
@@ -7891,7 +7891,7 @@
         <v>29042</v>
       </c>
       <c r="E443">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="444" spans="1:5">
@@ -7908,7 +7908,7 @@
         <v>29042</v>
       </c>
       <c r="E444">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="445" spans="1:5">
@@ -7925,7 +7925,7 @@
         <v>29042</v>
       </c>
       <c r="E445">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="446" spans="1:5">
@@ -7942,7 +7942,7 @@
         <v>29042</v>
       </c>
       <c r="E446">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="447" spans="1:5">
@@ -7959,7 +7959,7 @@
         <v>29042</v>
       </c>
       <c r="E447">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="448" spans="1:5">
@@ -7967,16 +7967,16 @@
         <v>447</v>
       </c>
       <c r="B448">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C448">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D448">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E448">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="449" spans="1:5">
@@ -7984,16 +7984,16 @@
         <v>448</v>
       </c>
       <c r="B449">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C449">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D449">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E449">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="450" spans="1:5">
@@ -8001,16 +8001,16 @@
         <v>449</v>
       </c>
       <c r="B450">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C450">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D450">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E450">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="451" spans="1:5">
@@ -8018,16 +8018,16 @@
         <v>450</v>
       </c>
       <c r="B451">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C451">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D451">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E451">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="452" spans="1:5">
@@ -8035,16 +8035,16 @@
         <v>451</v>
       </c>
       <c r="B452">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C452">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D452">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E452">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="453" spans="1:5">
@@ -8052,16 +8052,16 @@
         <v>452</v>
       </c>
       <c r="B453">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C453">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D453">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E453">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="454" spans="1:5">
@@ -8069,16 +8069,16 @@
         <v>453</v>
       </c>
       <c r="B454">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C454">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D454">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E454">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="455" spans="1:5">
@@ -8086,16 +8086,16 @@
         <v>454</v>
       </c>
       <c r="B455">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C455">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D455">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E455">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="456" spans="1:5">
@@ -8103,16 +8103,16 @@
         <v>455</v>
       </c>
       <c r="B456">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C456">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D456">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E456">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="457" spans="1:5">
@@ -8120,16 +8120,16 @@
         <v>456</v>
       </c>
       <c r="B457">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C457">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D457">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E457">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="458" spans="1:5">
@@ -8137,16 +8137,16 @@
         <v>457</v>
       </c>
       <c r="B458">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C458">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D458">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E458">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="459" spans="1:5">
@@ -8154,16 +8154,16 @@
         <v>458</v>
       </c>
       <c r="B459">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C459">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D459">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E459">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="460" spans="1:5">
@@ -8171,16 +8171,16 @@
         <v>459</v>
       </c>
       <c r="B460">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C460">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D460">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E460">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="461" spans="1:5">
@@ -8188,16 +8188,16 @@
         <v>460</v>
       </c>
       <c r="B461">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C461">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D461">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E461">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="462" spans="1:5">
@@ -8205,16 +8205,16 @@
         <v>461</v>
       </c>
       <c r="B462">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C462">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D462">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E462">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="463" spans="1:5">
@@ -8222,16 +8222,16 @@
         <v>462</v>
       </c>
       <c r="B463">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="C463">
-        <v>20338</v>
+        <v>20339</v>
       </c>
       <c r="D463">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="E463">
-        <v>64714</v>
+        <v>64718</v>
       </c>
     </row>
     <row r="464" spans="1:5">
@@ -8239,16 +8239,16 @@
         <v>463</v>
       </c>
       <c r="B464">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="C464">
-        <v>20338</v>
+        <v>20339</v>
       </c>
       <c r="D464">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="E464">
-        <v>64714</v>
+        <v>64718</v>
       </c>
     </row>
     <row r="465" spans="1:5">
@@ -8256,10 +8256,10 @@
         <v>464</v>
       </c>
       <c r="B465">
-        <v>7240</v>
+        <v>7245</v>
       </c>
       <c r="C465">
-        <v>13587</v>
+        <v>13589</v>
       </c>
       <c r="D465">
         <v>35027</v>
@@ -8273,16 +8273,16 @@
         <v>465</v>
       </c>
       <c r="B466">
-        <v>7427</v>
+        <v>7430</v>
       </c>
       <c r="C466">
-        <v>14137</v>
+        <v>14139</v>
       </c>
       <c r="D466">
-        <v>36363</v>
+        <v>36364</v>
       </c>
       <c r="E466">
-        <v>55177</v>
+        <v>55179</v>
       </c>
     </row>
     <row r="467" spans="1:5">
@@ -8290,16 +8290,16 @@
         <v>466</v>
       </c>
       <c r="B467">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="C467">
-        <v>20338</v>
+        <v>20339</v>
       </c>
       <c r="D467">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="E467">
-        <v>64714</v>
+        <v>64718</v>
       </c>
     </row>
     <row r="468" spans="1:5">
@@ -8307,16 +8307,16 @@
         <v>467</v>
       </c>
       <c r="B468">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C468">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D468">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E468">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="469" spans="1:5">
@@ -8324,16 +8324,16 @@
         <v>468</v>
       </c>
       <c r="B469">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C469">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D469">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E469">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="470" spans="1:5">
@@ -8341,16 +8341,16 @@
         <v>469</v>
       </c>
       <c r="B470">
-        <v>14586</v>
+        <v>14594</v>
       </c>
       <c r="C470">
-        <v>26743</v>
+        <v>26747</v>
       </c>
       <c r="D470">
-        <v>52864</v>
+        <v>52866</v>
       </c>
       <c r="E470">
-        <v>70373</v>
+        <v>70377</v>
       </c>
     </row>
     <row r="471" spans="1:5">
@@ -8358,16 +8358,16 @@
         <v>470</v>
       </c>
       <c r="B471">
-        <v>11208</v>
+        <v>11210</v>
       </c>
       <c r="C471">
-        <v>20338</v>
+        <v>20339</v>
       </c>
       <c r="D471">
-        <v>45651</v>
+        <v>45652</v>
       </c>
       <c r="E471">
-        <v>64714</v>
+        <v>64718</v>
       </c>
     </row>
     <row r="472" spans="1:5">
@@ -8375,16 +8375,16 @@
         <v>471</v>
       </c>
       <c r="B472">
-        <v>12692</v>
+        <v>12694</v>
       </c>
       <c r="C472">
-        <v>23050</v>
+        <v>23051</v>
       </c>
       <c r="D472">
-        <v>49148</v>
+        <v>49149</v>
       </c>
       <c r="E472">
-        <v>67872</v>
+        <v>67874</v>
       </c>
     </row>
     <row r="473" spans="1:5">
@@ -8392,16 +8392,16 @@
         <v>472</v>
       </c>
       <c r="B473">
-        <v>7427</v>
+        <v>7430</v>
       </c>
       <c r="C473">
-        <v>14137</v>
+        <v>14139</v>
       </c>
       <c r="D473">
-        <v>36363</v>
+        <v>36364</v>
       </c>
       <c r="E473">
-        <v>55177</v>
+        <v>55179</v>
       </c>
     </row>
     <row r="474" spans="1:5">
@@ -8409,16 +8409,16 @@
         <v>473</v>
       </c>
       <c r="B474">
-        <v>7427</v>
+        <v>7430</v>
       </c>
       <c r="C474">
-        <v>14137</v>
+        <v>14139</v>
       </c>
       <c r="D474">
-        <v>36363</v>
+        <v>36364</v>
       </c>
       <c r="E474">
-        <v>55177</v>
+        <v>55179</v>
       </c>
     </row>
     <row r="475" spans="1:5">
@@ -8429,13 +8429,13 @@
         <v>6882</v>
       </c>
       <c r="C475">
-        <v>14068</v>
+        <v>14069</v>
       </c>
       <c r="D475">
         <v>36969</v>
       </c>
       <c r="E475">
-        <v>55978</v>
+        <v>55984</v>
       </c>
     </row>
     <row r="476" spans="1:5">
@@ -8443,16 +8443,16 @@
         <v>475</v>
       </c>
       <c r="B476">
-        <v>6603</v>
+        <v>6606</v>
       </c>
       <c r="C476">
-        <v>13331</v>
+        <v>13332</v>
       </c>
       <c r="D476">
         <v>36069</v>
       </c>
       <c r="E476">
-        <v>55054</v>
+        <v>55059</v>
       </c>
     </row>
     <row r="477" spans="1:5">
@@ -8460,16 +8460,16 @@
         <v>476</v>
       </c>
       <c r="B477">
-        <v>6603</v>
+        <v>6606</v>
       </c>
       <c r="C477">
-        <v>13331</v>
+        <v>13332</v>
       </c>
       <c r="D477">
         <v>36069</v>
       </c>
       <c r="E477">
-        <v>55054</v>
+        <v>55059</v>
       </c>
     </row>
     <row r="478" spans="1:5">
@@ -8477,16 +8477,16 @@
         <v>477</v>
       </c>
       <c r="B478">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="C478">
-        <v>12767</v>
+        <v>12784</v>
       </c>
       <c r="D478">
-        <v>33248</v>
+        <v>33258</v>
       </c>
       <c r="E478">
-        <v>51759</v>
+        <v>51777</v>
       </c>
     </row>
     <row r="479" spans="1:5">
@@ -8494,16 +8494,16 @@
         <v>478</v>
       </c>
       <c r="B479">
-        <v>8613</v>
+        <v>8617</v>
       </c>
       <c r="C479">
-        <v>14650</v>
+        <v>14652</v>
       </c>
       <c r="D479">
         <v>37971</v>
       </c>
       <c r="E479">
-        <v>57950</v>
+        <v>57952</v>
       </c>
     </row>
     <row r="480" spans="1:5">
@@ -8511,13 +8511,13 @@
         <v>479</v>
       </c>
       <c r="B480">
-        <v>9133</v>
+        <v>9141</v>
       </c>
       <c r="C480">
-        <v>16142</v>
+        <v>16145</v>
       </c>
       <c r="D480">
-        <v>40372</v>
+        <v>40373</v>
       </c>
       <c r="E480">
         <v>60992</v>
@@ -8528,16 +8528,16 @@
         <v>480</v>
       </c>
       <c r="B481">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="C481">
-        <v>12767</v>
+        <v>12784</v>
       </c>
       <c r="D481">
-        <v>33248</v>
+        <v>33258</v>
       </c>
       <c r="E481">
-        <v>51759</v>
+        <v>51777</v>
       </c>
     </row>
     <row r="482" spans="1:5">
@@ -8545,16 +8545,16 @@
         <v>481</v>
       </c>
       <c r="B482">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="C482">
-        <v>12767</v>
+        <v>12784</v>
       </c>
       <c r="D482">
-        <v>33248</v>
+        <v>33258</v>
       </c>
       <c r="E482">
-        <v>51759</v>
+        <v>51777</v>
       </c>
     </row>
     <row r="483" spans="1:5">
@@ -8562,16 +8562,16 @@
         <v>482</v>
       </c>
       <c r="B483">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="C483">
-        <v>12767</v>
+        <v>12784</v>
       </c>
       <c r="D483">
-        <v>33248</v>
+        <v>33258</v>
       </c>
       <c r="E483">
-        <v>51759</v>
+        <v>51777</v>
       </c>
     </row>
     <row r="484" spans="1:5">
@@ -8579,16 +8579,16 @@
         <v>483</v>
       </c>
       <c r="B484">
-        <v>7888</v>
+        <v>7912</v>
       </c>
       <c r="C484">
-        <v>12767</v>
+        <v>12784</v>
       </c>
       <c r="D484">
-        <v>33248</v>
+        <v>33258</v>
       </c>
       <c r="E484">
-        <v>51759</v>
+        <v>51777</v>
       </c>
     </row>
     <row r="485" spans="1:5">
@@ -8596,13 +8596,13 @@
         <v>484</v>
       </c>
       <c r="B485">
-        <v>9133</v>
+        <v>9141</v>
       </c>
       <c r="C485">
-        <v>16142</v>
+        <v>16145</v>
       </c>
       <c r="D485">
-        <v>40372</v>
+        <v>40373</v>
       </c>
       <c r="E485">
         <v>60992</v>
@@ -8613,13 +8613,13 @@
         <v>485</v>
       </c>
       <c r="B486">
-        <v>9040</v>
+        <v>9043</v>
       </c>
       <c r="C486">
-        <v>15730</v>
+        <v>15732</v>
       </c>
       <c r="D486">
-        <v>39487</v>
+        <v>39488</v>
       </c>
       <c r="E486">
         <v>60039</v>
@@ -8630,16 +8630,16 @@
         <v>486</v>
       </c>
       <c r="B487">
-        <v>8242</v>
+        <v>8247</v>
       </c>
       <c r="C487">
-        <v>14018</v>
+        <v>14021</v>
       </c>
       <c r="D487">
-        <v>36613</v>
+        <v>36614</v>
       </c>
       <c r="E487">
-        <v>56172</v>
+        <v>56176</v>
       </c>
     </row>
     <row r="488" spans="1:5">
@@ -8653,10 +8653,10 @@
         <v>14376</v>
       </c>
       <c r="D488">
-        <v>36959</v>
+        <v>36960</v>
       </c>
       <c r="E488">
-        <v>56243</v>
+        <v>56247</v>
       </c>
     </row>
     <row r="489" spans="1:5">
@@ -8670,10 +8670,10 @@
         <v>14376</v>
       </c>
       <c r="D489">
-        <v>36959</v>
+        <v>36960</v>
       </c>
       <c r="E489">
-        <v>56243</v>
+        <v>56247</v>
       </c>
     </row>
     <row r="490" spans="1:5">
@@ -8681,13 +8681,13 @@
         <v>489</v>
       </c>
       <c r="B490">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="C490">
-        <v>24092</v>
+        <v>24096</v>
       </c>
       <c r="D490">
-        <v>50850</v>
+        <v>50852</v>
       </c>
       <c r="E490">
         <v>70327</v>
@@ -8698,16 +8698,16 @@
         <v>490</v>
       </c>
       <c r="B491">
-        <v>13393</v>
+        <v>13401</v>
       </c>
       <c r="C491">
-        <v>25206</v>
+        <v>25210</v>
       </c>
       <c r="D491">
-        <v>52722</v>
+        <v>52724</v>
       </c>
       <c r="E491">
-        <v>71253</v>
+        <v>71263</v>
       </c>
     </row>
     <row r="492" spans="1:5">
@@ -8715,13 +8715,13 @@
         <v>491</v>
       </c>
       <c r="B492">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="C492">
-        <v>24092</v>
+        <v>24096</v>
       </c>
       <c r="D492">
-        <v>50850</v>
+        <v>50852</v>
       </c>
       <c r="E492">
         <v>70327</v>
@@ -8732,13 +8732,13 @@
         <v>492</v>
       </c>
       <c r="B493">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="C493">
-        <v>24092</v>
+        <v>24096</v>
       </c>
       <c r="D493">
-        <v>50850</v>
+        <v>50852</v>
       </c>
       <c r="E493">
         <v>70327</v>
@@ -8749,13 +8749,13 @@
         <v>493</v>
       </c>
       <c r="B494">
-        <v>12892</v>
+        <v>12901</v>
       </c>
       <c r="C494">
-        <v>24092</v>
+        <v>24096</v>
       </c>
       <c r="D494">
-        <v>50850</v>
+        <v>50852</v>
       </c>
       <c r="E494">
         <v>70327</v>
@@ -8766,16 +8766,16 @@
         <v>494</v>
       </c>
       <c r="B495">
-        <v>12631</v>
+        <v>12637</v>
       </c>
       <c r="C495">
-        <v>26163</v>
+        <v>26166</v>
       </c>
       <c r="D495">
-        <v>54565</v>
+        <v>54574</v>
       </c>
       <c r="E495">
-        <v>72794</v>
+        <v>72812</v>
       </c>
     </row>
     <row r="496" spans="1:5">
@@ -8783,16 +8783,16 @@
         <v>495</v>
       </c>
       <c r="B496">
-        <v>14954</v>
+        <v>14967</v>
       </c>
       <c r="C496">
-        <v>29210</v>
+        <v>29216</v>
       </c>
       <c r="D496">
-        <v>57102</v>
+        <v>57110</v>
       </c>
       <c r="E496">
-        <v>74565</v>
+        <v>74585</v>
       </c>
     </row>
     <row r="497" spans="1:5">
@@ -8800,16 +8800,16 @@
         <v>496</v>
       </c>
       <c r="B497">
-        <v>12631</v>
+        <v>12637</v>
       </c>
       <c r="C497">
-        <v>26163</v>
+        <v>26166</v>
       </c>
       <c r="D497">
-        <v>54565</v>
+        <v>54574</v>
       </c>
       <c r="E497">
-        <v>72794</v>
+        <v>72812</v>
       </c>
     </row>
     <row r="498" spans="1:5">
@@ -8817,16 +8817,16 @@
         <v>497</v>
       </c>
       <c r="B498">
-        <v>13885</v>
+        <v>13888</v>
       </c>
       <c r="C498">
-        <v>26197</v>
+        <v>26201</v>
       </c>
       <c r="D498">
-        <v>52286</v>
+        <v>52296</v>
       </c>
       <c r="E498">
-        <v>69573</v>
+        <v>69590</v>
       </c>
     </row>
     <row r="499" spans="1:5">
@@ -8834,16 +8834,16 @@
         <v>498</v>
       </c>
       <c r="B499">
-        <v>13885</v>
+        <v>13888</v>
       </c>
       <c r="C499">
-        <v>26197</v>
+        <v>26201</v>
       </c>
       <c r="D499">
-        <v>52286</v>
+        <v>52296</v>
       </c>
       <c r="E499">
-        <v>69573</v>
+        <v>69590</v>
       </c>
     </row>
     <row r="500" spans="1:5">
@@ -8851,16 +8851,16 @@
         <v>499</v>
       </c>
       <c r="B500">
-        <v>13885</v>
+        <v>13888</v>
       </c>
       <c r="C500">
-        <v>26197</v>
+        <v>26201</v>
       </c>
       <c r="D500">
-        <v>52286</v>
+        <v>52296</v>
       </c>
       <c r="E500">
-        <v>69573</v>
+        <v>69590</v>
       </c>
     </row>
     <row r="501" spans="1:5">
@@ -8868,16 +8868,16 @@
         <v>500</v>
       </c>
       <c r="B501">
-        <v>8685</v>
+        <v>8686</v>
       </c>
       <c r="C501">
-        <v>15356</v>
+        <v>15357</v>
       </c>
       <c r="D501">
-        <v>38272</v>
+        <v>38273</v>
       </c>
       <c r="E501">
-        <v>57727</v>
+        <v>57733</v>
       </c>
     </row>
   </sheetData>
